--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -577,7 +577,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -598,8 +598,8 @@
     <col width="34.75" bestFit="1" customWidth="1" style="18" min="5" max="5"/>
     <col width="14.75" bestFit="1" customWidth="1" style="18" min="6" max="6"/>
     <col width="18.125" bestFit="1" customWidth="1" style="18" min="7" max="7"/>
-    <col width="9" customWidth="1" style="18" min="8" max="8"/>
-    <col width="9" customWidth="1" style="18" min="9" max="16384"/>
+    <col width="9" customWidth="1" style="18" min="8" max="9"/>
+    <col width="9" customWidth="1" style="18" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="10">
@@ -637,6 +637,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -646,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z51"/>
+  <dimension ref="A1:Z88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="8" min="1" max="1"/>
@@ -668,8 +669,8 @@
     <col width="7.625" bestFit="1" customWidth="1" style="21" min="20" max="20"/>
     <col width="12.625" customWidth="1" style="21" min="21" max="21"/>
     <col width="9" customWidth="1" style="21" min="22" max="26"/>
-    <col width="9" customWidth="1" style="18" min="27" max="27"/>
-    <col width="9" customWidth="1" style="18" min="28" max="16384"/>
+    <col width="9" customWidth="1" style="18" min="27" max="28"/>
+    <col width="9" customWidth="1" style="18" min="29" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
@@ -2311,6 +2312,1005 @@
         <v>300</v>
       </c>
       <c r="I51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>100</v>
+      </c>
+      <c r="C52" t="n">
+        <v>7101</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>101</v>
+      </c>
+      <c r="C53" t="n">
+        <v>7102</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>102</v>
+      </c>
+      <c r="C54" t="n">
+        <v>7103</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>103</v>
+      </c>
+      <c r="C55" t="n">
+        <v>7104</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>104</v>
+      </c>
+      <c r="C56" t="n">
+        <v>7105</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>105</v>
+      </c>
+      <c r="C57" t="n">
+        <v>7106</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>106</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7107</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>GoldKey</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>110</v>
+      </c>
+      <c r="C59" t="n">
+        <v>7201</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>111</v>
+      </c>
+      <c r="C60" t="n">
+        <v>7202</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>112</v>
+      </c>
+      <c r="C61" t="n">
+        <v>7203</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>113</v>
+      </c>
+      <c r="C62" t="n">
+        <v>7204</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>114</v>
+      </c>
+      <c r="C63" t="n">
+        <v>7205</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>100</v>
+      </c>
+      <c r="H63" t="n">
+        <v>100</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>115</v>
+      </c>
+      <c r="C64" t="n">
+        <v>7206</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>116</v>
+      </c>
+      <c r="C65" t="n">
+        <v>7207</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>117</v>
+      </c>
+      <c r="C66" t="n">
+        <v>7208</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>5</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>118</v>
+      </c>
+      <c r="C67" t="n">
+        <v>7209</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>119</v>
+      </c>
+      <c r="C68" t="n">
+        <v>7210</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>150</v>
+      </c>
+      <c r="H68" t="n">
+        <v>150</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>120</v>
+      </c>
+      <c r="C69" t="n">
+        <v>7211</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>121</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7212</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>122</v>
+      </c>
+      <c r="C71" t="n">
+        <v>7213</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>123</v>
+      </c>
+      <c r="C72" t="n">
+        <v>7214</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>124</v>
+      </c>
+      <c r="C73" t="n">
+        <v>7215</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>BronzeKey</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>125</v>
+      </c>
+      <c r="C74" t="n">
+        <v>7216</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H74" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>126</v>
+      </c>
+      <c r="C75" t="n">
+        <v>7217</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>127</v>
+      </c>
+      <c r="C76" t="n">
+        <v>7218</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" t="n">
+        <v>10</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>128</v>
+      </c>
+      <c r="C77" t="n">
+        <v>7219</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>5</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>129</v>
+      </c>
+      <c r="C78" t="n">
+        <v>7220</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SilverKey</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>130</v>
+      </c>
+      <c r="C79" t="n">
+        <v>7221</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H79" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>131</v>
+      </c>
+      <c r="C80" t="n">
+        <v>7222</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>10</v>
+      </c>
+      <c r="H80" t="n">
+        <v>10</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>132</v>
+      </c>
+      <c r="C81" t="n">
+        <v>7223</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>133</v>
+      </c>
+      <c r="C82" t="n">
+        <v>7224</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>8</v>
+      </c>
+      <c r="H82" t="n">
+        <v>8</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>134</v>
+      </c>
+      <c r="C83" t="n">
+        <v>7225</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>300</v>
+      </c>
+      <c r="H83" t="n">
+        <v>300</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>135</v>
+      </c>
+      <c r="C84" t="n">
+        <v>7226</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H84" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>136</v>
+      </c>
+      <c r="C85" t="n">
+        <v>7227</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>137</v>
+      </c>
+      <c r="C86" t="n">
+        <v>7228</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>15</v>
+      </c>
+      <c r="H86" t="n">
+        <v>15</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>138</v>
+      </c>
+      <c r="C87" t="n">
+        <v>7229</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H87" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>139</v>
+      </c>
+      <c r="C88" t="n">
+        <v>7230</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>GoldKey</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>5</v>
+      </c>
+      <c r="I88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2352,8 +3352,8 @@
     <col width="7.625" bestFit="1" customWidth="1" style="21" min="22" max="22"/>
     <col width="12.625" customWidth="1" style="21" min="23" max="23"/>
     <col width="9" customWidth="1" style="21" min="24" max="28"/>
-    <col width="9" customWidth="1" style="18" min="29" max="29"/>
-    <col width="9" customWidth="1" style="18" min="30" max="16384"/>
+    <col width="9" customWidth="1" style="18" min="29" max="30"/>
+    <col width="9" customWidth="1" style="18" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">

--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z88"/>
+  <dimension ref="A1:Z92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="8" min="1" max="1"/>
@@ -3312,6 +3312,113 @@
       </c>
       <c r="I88" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>200</v>
+      </c>
+      <c r="C89" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>100</v>
+      </c>
+      <c r="H89" t="n">
+        <v>300</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>201</v>
+      </c>
+      <c r="C90" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>202</v>
+      </c>
+      <c r="C91" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1030100001</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>203</v>
+      </c>
+      <c r="C92" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ItemPool</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F92" t="n">
+        <v>10001</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z92"/>
+  <dimension ref="A1:Z192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="8" min="1" max="1"/>
@@ -3419,6 +3419,2706 @@
       </c>
       <c r="I92" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>300</v>
+      </c>
+      <c r="C93" t="n">
+        <v>7501</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>301</v>
+      </c>
+      <c r="C94" t="n">
+        <v>7502</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>3</v>
+      </c>
+      <c r="H94" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>302</v>
+      </c>
+      <c r="C95" t="n">
+        <v>7503</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>3</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>303</v>
+      </c>
+      <c r="C96" t="n">
+        <v>7504</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>5</v>
+      </c>
+      <c r="H96" t="n">
+        <v>5</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>304</v>
+      </c>
+      <c r="C97" t="n">
+        <v>7505</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>50</v>
+      </c>
+      <c r="H97" t="n">
+        <v>50</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>305</v>
+      </c>
+      <c r="C98" t="n">
+        <v>7506</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>306</v>
+      </c>
+      <c r="C99" t="n">
+        <v>7507</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>307</v>
+      </c>
+      <c r="C100" t="n">
+        <v>7508</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>3</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>308</v>
+      </c>
+      <c r="C101" t="n">
+        <v>7509</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" t="n">
+        <v>5</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>309</v>
+      </c>
+      <c r="C102" t="n">
+        <v>7510</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>100</v>
+      </c>
+      <c r="H102" t="n">
+        <v>100</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>310</v>
+      </c>
+      <c r="C103" t="n">
+        <v>7511</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>311</v>
+      </c>
+      <c r="C104" t="n">
+        <v>7512</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>3</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>312</v>
+      </c>
+      <c r="C105" t="n">
+        <v>7513</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>313</v>
+      </c>
+      <c r="C106" t="n">
+        <v>7514</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>5</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>314</v>
+      </c>
+      <c r="C107" t="n">
+        <v>7515</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>50</v>
+      </c>
+      <c r="H107" t="n">
+        <v>50</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>315</v>
+      </c>
+      <c r="C108" t="n">
+        <v>7516</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>316</v>
+      </c>
+      <c r="C109" t="n">
+        <v>7517</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>317</v>
+      </c>
+      <c r="C110" t="n">
+        <v>7518</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>3</v>
+      </c>
+      <c r="H110" t="n">
+        <v>3</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>318</v>
+      </c>
+      <c r="C111" t="n">
+        <v>7519</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>5</v>
+      </c>
+      <c r="H111" t="n">
+        <v>5</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>319</v>
+      </c>
+      <c r="C112" t="n">
+        <v>7520</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>100</v>
+      </c>
+      <c r="H112" t="n">
+        <v>100</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>320</v>
+      </c>
+      <c r="C113" t="n">
+        <v>7521</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>321</v>
+      </c>
+      <c r="C114" t="n">
+        <v>7522</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>322</v>
+      </c>
+      <c r="C115" t="n">
+        <v>7523</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>3</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>323</v>
+      </c>
+      <c r="C116" t="n">
+        <v>7524</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>5</v>
+      </c>
+      <c r="H116" t="n">
+        <v>5</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>324</v>
+      </c>
+      <c r="C117" t="n">
+        <v>7525</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>50</v>
+      </c>
+      <c r="H117" t="n">
+        <v>50</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>325</v>
+      </c>
+      <c r="C118" t="n">
+        <v>7526</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>326</v>
+      </c>
+      <c r="C119" t="n">
+        <v>7527</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>327</v>
+      </c>
+      <c r="C120" t="n">
+        <v>7528</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" t="n">
+        <v>3</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>328</v>
+      </c>
+      <c r="C121" t="n">
+        <v>7529</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>5</v>
+      </c>
+      <c r="H121" t="n">
+        <v>5</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>329</v>
+      </c>
+      <c r="C122" t="n">
+        <v>7530</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>100</v>
+      </c>
+      <c r="H122" t="n">
+        <v>100</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>330</v>
+      </c>
+      <c r="C123" t="n">
+        <v>7531</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H123" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>331</v>
+      </c>
+      <c r="C124" t="n">
+        <v>7532</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>332</v>
+      </c>
+      <c r="C125" t="n">
+        <v>7533</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>333</v>
+      </c>
+      <c r="C126" t="n">
+        <v>7534</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>5</v>
+      </c>
+      <c r="H126" t="n">
+        <v>5</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>334</v>
+      </c>
+      <c r="C127" t="n">
+        <v>7535</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>50</v>
+      </c>
+      <c r="H127" t="n">
+        <v>50</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>335</v>
+      </c>
+      <c r="C128" t="n">
+        <v>7536</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H128" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>336</v>
+      </c>
+      <c r="C129" t="n">
+        <v>7537</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H129" t="n">
+        <v>3</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>337</v>
+      </c>
+      <c r="C130" t="n">
+        <v>7538</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>3</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>338</v>
+      </c>
+      <c r="C131" t="n">
+        <v>7539</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>5</v>
+      </c>
+      <c r="H131" t="n">
+        <v>5</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>339</v>
+      </c>
+      <c r="C132" t="n">
+        <v>7540</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>100</v>
+      </c>
+      <c r="H132" t="n">
+        <v>100</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>340</v>
+      </c>
+      <c r="C133" t="n">
+        <v>7541</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H133" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>341</v>
+      </c>
+      <c r="C134" t="n">
+        <v>7542</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>342</v>
+      </c>
+      <c r="C135" t="n">
+        <v>7543</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>3</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>343</v>
+      </c>
+      <c r="C136" t="n">
+        <v>7544</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>5</v>
+      </c>
+      <c r="H136" t="n">
+        <v>5</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>344</v>
+      </c>
+      <c r="C137" t="n">
+        <v>7545</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>50</v>
+      </c>
+      <c r="H137" t="n">
+        <v>50</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>345</v>
+      </c>
+      <c r="C138" t="n">
+        <v>7546</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>346</v>
+      </c>
+      <c r="C139" t="n">
+        <v>7547</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>WeaponScroll</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>3</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>7548</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>ArmorScroll</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>3</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>348</v>
+      </c>
+      <c r="C141" t="n">
+        <v>7549</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MagicCrystal</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>5</v>
+      </c>
+      <c r="H141" t="n">
+        <v>5</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>349</v>
+      </c>
+      <c r="C142" t="n">
+        <v>7550</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>100</v>
+      </c>
+      <c r="H142" t="n">
+        <v>100</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>400</v>
+      </c>
+      <c r="C143" t="n">
+        <v>7601</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H143" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>401</v>
+      </c>
+      <c r="C144" t="n">
+        <v>7602</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>5</v>
+      </c>
+      <c r="H144" t="n">
+        <v>5</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>402</v>
+      </c>
+      <c r="C145" t="n">
+        <v>7603</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>5</v>
+      </c>
+      <c r="H145" t="n">
+        <v>5</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>403</v>
+      </c>
+      <c r="C146" t="n">
+        <v>7604</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>404</v>
+      </c>
+      <c r="C147" t="n">
+        <v>7605</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>300</v>
+      </c>
+      <c r="H147" t="n">
+        <v>300</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>405</v>
+      </c>
+      <c r="C148" t="n">
+        <v>7606</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H148" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>406</v>
+      </c>
+      <c r="C149" t="n">
+        <v>7607</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>5</v>
+      </c>
+      <c r="H149" t="n">
+        <v>5</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>407</v>
+      </c>
+      <c r="C150" t="n">
+        <v>7608</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>5</v>
+      </c>
+      <c r="H150" t="n">
+        <v>5</v>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>408</v>
+      </c>
+      <c r="C151" t="n">
+        <v>7609</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>3</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>409</v>
+      </c>
+      <c r="C152" t="n">
+        <v>7610</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>GoldKey</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>3</v>
+      </c>
+      <c r="H152" t="n">
+        <v>3</v>
+      </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>410</v>
+      </c>
+      <c r="C153" t="n">
+        <v>7611</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H153" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>411</v>
+      </c>
+      <c r="C154" t="n">
+        <v>7612</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>5</v>
+      </c>
+      <c r="H154" t="n">
+        <v>5</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>412</v>
+      </c>
+      <c r="C155" t="n">
+        <v>7613</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>5</v>
+      </c>
+      <c r="H155" t="n">
+        <v>5</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>413</v>
+      </c>
+      <c r="C156" t="n">
+        <v>7614</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>3</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>414</v>
+      </c>
+      <c r="C157" t="n">
+        <v>7615</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>300</v>
+      </c>
+      <c r="H157" t="n">
+        <v>300</v>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>415</v>
+      </c>
+      <c r="C158" t="n">
+        <v>7616</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H158" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>416</v>
+      </c>
+      <c r="C159" t="n">
+        <v>7617</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>5</v>
+      </c>
+      <c r="H159" t="n">
+        <v>5</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>417</v>
+      </c>
+      <c r="C160" t="n">
+        <v>7618</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>5</v>
+      </c>
+      <c r="H160" t="n">
+        <v>5</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>418</v>
+      </c>
+      <c r="C161" t="n">
+        <v>7619</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>3</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>419</v>
+      </c>
+      <c r="C162" t="n">
+        <v>7620</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>GoldKey</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>3</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>420</v>
+      </c>
+      <c r="C163" t="n">
+        <v>7621</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H163" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>421</v>
+      </c>
+      <c r="C164" t="n">
+        <v>7622</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>5</v>
+      </c>
+      <c r="H164" t="n">
+        <v>5</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>422</v>
+      </c>
+      <c r="C165" t="n">
+        <v>7623</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>5</v>
+      </c>
+      <c r="H165" t="n">
+        <v>5</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>423</v>
+      </c>
+      <c r="C166" t="n">
+        <v>7624</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>3</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>424</v>
+      </c>
+      <c r="C167" t="n">
+        <v>7625</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>300</v>
+      </c>
+      <c r="H167" t="n">
+        <v>300</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>425</v>
+      </c>
+      <c r="C168" t="n">
+        <v>7626</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H168" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>426</v>
+      </c>
+      <c r="C169" t="n">
+        <v>7627</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>5</v>
+      </c>
+      <c r="H169" t="n">
+        <v>5</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>427</v>
+      </c>
+      <c r="C170" t="n">
+        <v>7628</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>5</v>
+      </c>
+      <c r="H170" t="n">
+        <v>5</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>428</v>
+      </c>
+      <c r="C171" t="n">
+        <v>7629</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>3</v>
+      </c>
+      <c r="H171" t="n">
+        <v>3</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>429</v>
+      </c>
+      <c r="C172" t="n">
+        <v>7630</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>GoldKey</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="n">
+        <v>3</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>430</v>
+      </c>
+      <c r="C173" t="n">
+        <v>7631</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H173" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>431</v>
+      </c>
+      <c r="C174" t="n">
+        <v>7632</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>5</v>
+      </c>
+      <c r="H174" t="n">
+        <v>5</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>432</v>
+      </c>
+      <c r="C175" t="n">
+        <v>7633</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>5</v>
+      </c>
+      <c r="H175" t="n">
+        <v>5</v>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>433</v>
+      </c>
+      <c r="C176" t="n">
+        <v>7634</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>3</v>
+      </c>
+      <c r="H176" t="n">
+        <v>3</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>434</v>
+      </c>
+      <c r="C177" t="n">
+        <v>7635</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>300</v>
+      </c>
+      <c r="H177" t="n">
+        <v>300</v>
+      </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>435</v>
+      </c>
+      <c r="C178" t="n">
+        <v>7636</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H178" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>436</v>
+      </c>
+      <c r="C179" t="n">
+        <v>7637</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>5</v>
+      </c>
+      <c r="H179" t="n">
+        <v>5</v>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>437</v>
+      </c>
+      <c r="C180" t="n">
+        <v>7638</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>5</v>
+      </c>
+      <c r="H180" t="n">
+        <v>5</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>438</v>
+      </c>
+      <c r="C181" t="n">
+        <v>7639</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>3</v>
+      </c>
+      <c r="H181" t="n">
+        <v>3</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>439</v>
+      </c>
+      <c r="C182" t="n">
+        <v>7640</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>GoldKey</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>3</v>
+      </c>
+      <c r="H182" t="n">
+        <v>3</v>
+      </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>440</v>
+      </c>
+      <c r="C183" t="n">
+        <v>7641</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H183" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>441</v>
+      </c>
+      <c r="C184" t="n">
+        <v>7642</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>5</v>
+      </c>
+      <c r="H184" t="n">
+        <v>5</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>442</v>
+      </c>
+      <c r="C185" t="n">
+        <v>7643</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>5</v>
+      </c>
+      <c r="H185" t="n">
+        <v>5</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>443</v>
+      </c>
+      <c r="C186" t="n">
+        <v>7644</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>3</v>
+      </c>
+      <c r="H186" t="n">
+        <v>3</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>444</v>
+      </c>
+      <c r="C187" t="n">
+        <v>7645</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>300</v>
+      </c>
+      <c r="H187" t="n">
+        <v>300</v>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>445</v>
+      </c>
+      <c r="C188" t="n">
+        <v>7646</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H188" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>446</v>
+      </c>
+      <c r="C189" t="n">
+        <v>7647</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AccessoryScroll</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>5</v>
+      </c>
+      <c r="H189" t="n">
+        <v>5</v>
+      </c>
+      <c r="I189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>447</v>
+      </c>
+      <c r="C190" t="n">
+        <v>7648</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>PromotionStone</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>5</v>
+      </c>
+      <c r="H190" t="n">
+        <v>5</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>448</v>
+      </c>
+      <c r="C191" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>TransferStone</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>3</v>
+      </c>
+      <c r="H191" t="n">
+        <v>3</v>
+      </c>
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>449</v>
+      </c>
+      <c r="C192" t="n">
+        <v>7650</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>GoldKey</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>3</v>
+      </c>
+      <c r="H192" t="n">
+        <v>3</v>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="58">
   <si>
     <t>!Enum</t>
   </si>
@@ -178,6 +178,22 @@
   </si>
   <si>
     <t>SkillBook</t>
+  </si>
+  <si>
+    <t>ItemPool</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArmorScroll</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -681,7 +697,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -734,7 +750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z200"/>
+  <dimension ref="A1:Z214"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="8" customWidth="1"/>
@@ -5627,6 +5643,340 @@
         <v>8000</v>
       </c>
       <c r="I200" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B201" s="18">
+        <v>458</v>
+      </c>
+      <c r="C201" s="18">
+        <v>8201</v>
+      </c>
+      <c r="D201" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E201" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F201" s="18">
+        <v>40001</v>
+      </c>
+      <c r="G201" s="18">
+        <v>1</v>
+      </c>
+      <c r="H201" s="18">
+        <v>1</v>
+      </c>
+      <c r="I201" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B202" s="18">
+        <v>459</v>
+      </c>
+      <c r="C202" s="18">
+        <v>8202</v>
+      </c>
+      <c r="D202" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E202" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G202" s="18">
+        <v>1000</v>
+      </c>
+      <c r="H202" s="18">
+        <v>2000</v>
+      </c>
+      <c r="I202" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B203" s="18">
+        <v>460</v>
+      </c>
+      <c r="C203" s="18">
+        <v>8203</v>
+      </c>
+      <c r="D203" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E203" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G203" s="18">
+        <v>3</v>
+      </c>
+      <c r="H203" s="18">
+        <v>5</v>
+      </c>
+      <c r="I203" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B204" s="18">
+        <v>461</v>
+      </c>
+      <c r="C204" s="18">
+        <v>8203</v>
+      </c>
+      <c r="D204" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E204" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G204" s="18">
+        <v>3</v>
+      </c>
+      <c r="H204" s="18">
+        <v>5</v>
+      </c>
+      <c r="I204" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B205" s="18">
+        <v>462</v>
+      </c>
+      <c r="C205" s="18">
+        <v>8203</v>
+      </c>
+      <c r="D205" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E205" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G205" s="18">
+        <v>3</v>
+      </c>
+      <c r="H205" s="18">
+        <v>5</v>
+      </c>
+      <c r="I205" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B206" s="18">
+        <v>463</v>
+      </c>
+      <c r="C206" s="18">
+        <v>8211</v>
+      </c>
+      <c r="D206" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E206" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F206" s="18">
+        <v>40002</v>
+      </c>
+      <c r="G206" s="18">
+        <v>1</v>
+      </c>
+      <c r="H206" s="18">
+        <v>1</v>
+      </c>
+      <c r="I206" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B207" s="18">
+        <v>464</v>
+      </c>
+      <c r="C207" s="18">
+        <v>8212</v>
+      </c>
+      <c r="D207" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E207" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G207" s="18">
+        <v>3000</v>
+      </c>
+      <c r="H207" s="18">
+        <v>5000</v>
+      </c>
+      <c r="I207" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B208" s="18">
+        <v>465</v>
+      </c>
+      <c r="C208" s="18">
+        <v>8213</v>
+      </c>
+      <c r="D208" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E208" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G208" s="18">
+        <v>8</v>
+      </c>
+      <c r="H208" s="18">
+        <v>12</v>
+      </c>
+      <c r="I208" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B209" s="18">
+        <v>466</v>
+      </c>
+      <c r="C209" s="18">
+        <v>8213</v>
+      </c>
+      <c r="D209" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E209" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G209" s="18">
+        <v>8</v>
+      </c>
+      <c r="H209" s="18">
+        <v>12</v>
+      </c>
+      <c r="I209" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B210" s="18">
+        <v>467</v>
+      </c>
+      <c r="C210" s="18">
+        <v>8213</v>
+      </c>
+      <c r="D210" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E210" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G210" s="18">
+        <v>8</v>
+      </c>
+      <c r="H210" s="18">
+        <v>12</v>
+      </c>
+      <c r="I210" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B211" s="18">
+        <v>468</v>
+      </c>
+      <c r="C211" s="18">
+        <v>8003</v>
+      </c>
+      <c r="D211" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E211" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F211" s="18">
+        <v>40003</v>
+      </c>
+      <c r="G211" s="18">
+        <v>1</v>
+      </c>
+      <c r="H211" s="18">
+        <v>1</v>
+      </c>
+      <c r="I211" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B212" s="18">
+        <v>469</v>
+      </c>
+      <c r="C212" s="18">
+        <v>8003</v>
+      </c>
+      <c r="D212" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E212" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G212" s="18">
+        <v>1000</v>
+      </c>
+      <c r="H212" s="18">
+        <v>2000</v>
+      </c>
+      <c r="I212" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B213" s="18">
+        <v>470</v>
+      </c>
+      <c r="C213" s="18">
+        <v>8004</v>
+      </c>
+      <c r="D213" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E213" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F213" s="18">
+        <v>40003</v>
+      </c>
+      <c r="G213" s="18">
+        <v>1</v>
+      </c>
+      <c r="H213" s="18">
+        <v>1</v>
+      </c>
+      <c r="I213" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B214" s="18">
+        <v>471</v>
+      </c>
+      <c r="C214" s="18">
+        <v>8004</v>
+      </c>
+      <c r="D214" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E214" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G214" s="18">
+        <v>2000</v>
+      </c>
+      <c r="H214" s="18">
+        <v>4000</v>
+      </c>
+      <c r="I214" s="18">
         <v>1</v>
       </c>
     </row>

--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="59">
   <si>
     <t>!Enum</t>
   </si>
@@ -194,6 +194,9 @@
   <si>
     <t>ArmorScroll</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
   </si>
 </sst>
 </file>
@@ -697,7 +700,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -750,7 +753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z214"/>
+  <dimension ref="A1:Z250"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="8" customWidth="1"/>
@@ -5836,7 +5839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B209" s="18">
         <v>466</v>
       </c>
@@ -5859,7 +5862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B210" s="18">
         <v>467</v>
       </c>
@@ -5882,7 +5885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B211" s="18">
         <v>468</v>
       </c>
@@ -5908,7 +5911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B212" s="18">
         <v>469</v>
       </c>
@@ -5931,7 +5934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B213" s="18">
         <v>470</v>
       </c>
@@ -5957,7 +5960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B214" s="18">
         <v>471</v>
       </c>
@@ -5978,6 +5981,903 @@
       </c>
       <c r="I214" s="18">
         <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B215" s="18">
+        <v>472</v>
+      </c>
+      <c r="C215" s="18">
+        <v>100</v>
+      </c>
+      <c r="D215" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E215" s="18">
+        <v>1010101001</v>
+      </c>
+      <c r="G215" s="18">
+        <v>1</v>
+      </c>
+      <c r="H215" s="18">
+        <v>1</v>
+      </c>
+      <c r="I215" s="18">
+        <v>1</v>
+      </c>
+      <c r="J215" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K215" s="18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="216" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B216" s="18">
+        <v>473</v>
+      </c>
+      <c r="C216" s="18">
+        <v>100</v>
+      </c>
+      <c r="D216" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E216" s="18">
+        <v>1010101002</v>
+      </c>
+      <c r="G216" s="18">
+        <v>1</v>
+      </c>
+      <c r="H216" s="18">
+        <v>1</v>
+      </c>
+      <c r="I216" s="18">
+        <v>1</v>
+      </c>
+      <c r="J216" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K216" s="18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="217" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B217" s="18">
+        <v>474</v>
+      </c>
+      <c r="C217" s="18">
+        <v>100</v>
+      </c>
+      <c r="D217" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E217" s="18">
+        <v>1010101003</v>
+      </c>
+      <c r="G217" s="18">
+        <v>1</v>
+      </c>
+      <c r="H217" s="18">
+        <v>1</v>
+      </c>
+      <c r="I217" s="18">
+        <v>1</v>
+      </c>
+      <c r="J217" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K217" s="18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="218" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B218" s="18">
+        <v>475</v>
+      </c>
+      <c r="C218" s="18">
+        <v>100</v>
+      </c>
+      <c r="D218" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E218" s="18">
+        <v>1010101004</v>
+      </c>
+      <c r="G218" s="18">
+        <v>1</v>
+      </c>
+      <c r="H218" s="18">
+        <v>1</v>
+      </c>
+      <c r="I218" s="18">
+        <v>1</v>
+      </c>
+      <c r="J218" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K218" s="18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="219" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B219" s="18">
+        <v>476</v>
+      </c>
+      <c r="C219" s="18">
+        <v>100</v>
+      </c>
+      <c r="D219" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E219" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G219" s="18">
+        <v>100000</v>
+      </c>
+      <c r="H219" s="18">
+        <v>100000</v>
+      </c>
+      <c r="I219" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B220" s="18">
+        <v>477</v>
+      </c>
+      <c r="C220" s="18">
+        <v>100</v>
+      </c>
+      <c r="D220" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E220" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G220" s="18">
+        <v>10000</v>
+      </c>
+      <c r="H220" s="18">
+        <v>10000</v>
+      </c>
+      <c r="I220" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B221" s="18">
+        <v>478</v>
+      </c>
+      <c r="C221" s="18">
+        <v>8301</v>
+      </c>
+      <c r="D221" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E221" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G221" s="18">
+        <v>2000</v>
+      </c>
+      <c r="H221" s="18">
+        <v>3000</v>
+      </c>
+      <c r="I221" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B222" s="18">
+        <v>479</v>
+      </c>
+      <c r="C222" s="18">
+        <v>8301</v>
+      </c>
+      <c r="D222" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E222" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F222" s="18">
+        <v>10001</v>
+      </c>
+      <c r="G222" s="18">
+        <v>1</v>
+      </c>
+      <c r="H222" s="18">
+        <v>1</v>
+      </c>
+      <c r="I222" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="223" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B223" s="18">
+        <v>480</v>
+      </c>
+      <c r="C223" s="18">
+        <v>8302</v>
+      </c>
+      <c r="D223" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E223" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G223" s="18">
+        <v>4000</v>
+      </c>
+      <c r="H223" s="18">
+        <v>6000</v>
+      </c>
+      <c r="I223" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B224" s="18">
+        <v>481</v>
+      </c>
+      <c r="C224" s="18">
+        <v>8302</v>
+      </c>
+      <c r="D224" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E224" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F224" s="18">
+        <v>10001</v>
+      </c>
+      <c r="G224" s="18">
+        <v>1</v>
+      </c>
+      <c r="H224" s="18">
+        <v>1</v>
+      </c>
+      <c r="I224" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="225" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B225" s="18">
+        <v>482</v>
+      </c>
+      <c r="C225" s="18">
+        <v>8303</v>
+      </c>
+      <c r="D225" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E225" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G225" s="18">
+        <v>6000</v>
+      </c>
+      <c r="H225" s="18">
+        <v>9000</v>
+      </c>
+      <c r="I225" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B226" s="18">
+        <v>483</v>
+      </c>
+      <c r="C226" s="18">
+        <v>8303</v>
+      </c>
+      <c r="D226" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E226" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F226" s="18">
+        <v>10001</v>
+      </c>
+      <c r="G226" s="18">
+        <v>1</v>
+      </c>
+      <c r="H226" s="18">
+        <v>1</v>
+      </c>
+      <c r="I226" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="227" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B227" s="18">
+        <v>484</v>
+      </c>
+      <c r="C227" s="18">
+        <v>8304</v>
+      </c>
+      <c r="D227" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E227" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G227" s="18">
+        <v>8000</v>
+      </c>
+      <c r="H227" s="18">
+        <v>12000</v>
+      </c>
+      <c r="I227" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B228" s="18">
+        <v>485</v>
+      </c>
+      <c r="C228" s="18">
+        <v>8304</v>
+      </c>
+      <c r="D228" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E228" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F228" s="18">
+        <v>10001</v>
+      </c>
+      <c r="G228" s="18">
+        <v>1</v>
+      </c>
+      <c r="H228" s="18">
+        <v>1</v>
+      </c>
+      <c r="I228" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="229" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B229" s="18">
+        <v>486</v>
+      </c>
+      <c r="C229" s="18">
+        <v>8305</v>
+      </c>
+      <c r="D229" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E229" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G229" s="18">
+        <v>10000</v>
+      </c>
+      <c r="H229" s="18">
+        <v>15000</v>
+      </c>
+      <c r="I229" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B230" s="18">
+        <v>487</v>
+      </c>
+      <c r="C230" s="18">
+        <v>8305</v>
+      </c>
+      <c r="D230" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E230" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F230" s="18">
+        <v>10001</v>
+      </c>
+      <c r="G230" s="18">
+        <v>1</v>
+      </c>
+      <c r="H230" s="18">
+        <v>1</v>
+      </c>
+      <c r="I230" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="231" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B231" s="18">
+        <v>488</v>
+      </c>
+      <c r="C231" s="18">
+        <v>8306</v>
+      </c>
+      <c r="D231" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E231" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G231" s="18">
+        <v>12000</v>
+      </c>
+      <c r="H231" s="18">
+        <v>18000</v>
+      </c>
+      <c r="I231" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B232" s="18">
+        <v>489</v>
+      </c>
+      <c r="C232" s="18">
+        <v>8306</v>
+      </c>
+      <c r="D232" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E232" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F232" s="18">
+        <v>10002</v>
+      </c>
+      <c r="G232" s="18">
+        <v>1</v>
+      </c>
+      <c r="H232" s="18">
+        <v>1</v>
+      </c>
+      <c r="I232" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="233" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B233" s="18">
+        <v>490</v>
+      </c>
+      <c r="C233" s="18">
+        <v>8307</v>
+      </c>
+      <c r="D233" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E233" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G233" s="18">
+        <v>14000</v>
+      </c>
+      <c r="H233" s="18">
+        <v>21000</v>
+      </c>
+      <c r="I233" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B234" s="18">
+        <v>491</v>
+      </c>
+      <c r="C234" s="18">
+        <v>8307</v>
+      </c>
+      <c r="D234" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E234" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F234" s="18">
+        <v>10002</v>
+      </c>
+      <c r="G234" s="18">
+        <v>1</v>
+      </c>
+      <c r="H234" s="18">
+        <v>1</v>
+      </c>
+      <c r="I234" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="235" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B235" s="18">
+        <v>492</v>
+      </c>
+      <c r="C235" s="18">
+        <v>8308</v>
+      </c>
+      <c r="D235" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E235" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G235" s="18">
+        <v>16000</v>
+      </c>
+      <c r="H235" s="18">
+        <v>24000</v>
+      </c>
+      <c r="I235" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B236" s="18">
+        <v>493</v>
+      </c>
+      <c r="C236" s="18">
+        <v>8308</v>
+      </c>
+      <c r="D236" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E236" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F236" s="18">
+        <v>10002</v>
+      </c>
+      <c r="G236" s="18">
+        <v>1</v>
+      </c>
+      <c r="H236" s="18">
+        <v>1</v>
+      </c>
+      <c r="I236" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="237" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B237" s="18">
+        <v>494</v>
+      </c>
+      <c r="C237" s="18">
+        <v>8309</v>
+      </c>
+      <c r="D237" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E237" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G237" s="18">
+        <v>18000</v>
+      </c>
+      <c r="H237" s="18">
+        <v>27000</v>
+      </c>
+      <c r="I237" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B238" s="18">
+        <v>495</v>
+      </c>
+      <c r="C238" s="18">
+        <v>8309</v>
+      </c>
+      <c r="D238" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E238" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F238" s="18">
+        <v>10002</v>
+      </c>
+      <c r="G238" s="18">
+        <v>1</v>
+      </c>
+      <c r="H238" s="18">
+        <v>1</v>
+      </c>
+      <c r="I238" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="239" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B239" s="18">
+        <v>496</v>
+      </c>
+      <c r="C239" s="18">
+        <v>8310</v>
+      </c>
+      <c r="D239" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E239" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G239" s="18">
+        <v>20000</v>
+      </c>
+      <c r="H239" s="18">
+        <v>30000</v>
+      </c>
+      <c r="I239" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B240" s="18">
+        <v>497</v>
+      </c>
+      <c r="C240" s="18">
+        <v>8310</v>
+      </c>
+      <c r="D240" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E240" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F240" s="18">
+        <v>10002</v>
+      </c>
+      <c r="G240" s="18">
+        <v>1</v>
+      </c>
+      <c r="H240" s="18">
+        <v>1</v>
+      </c>
+      <c r="I240" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="241" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B241" s="18">
+        <v>498</v>
+      </c>
+      <c r="C241" s="18">
+        <v>8311</v>
+      </c>
+      <c r="D241" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E241" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G241" s="18">
+        <v>22000</v>
+      </c>
+      <c r="H241" s="18">
+        <v>33000</v>
+      </c>
+      <c r="I241" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B242" s="18">
+        <v>499</v>
+      </c>
+      <c r="C242" s="18">
+        <v>8311</v>
+      </c>
+      <c r="D242" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E242" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F242" s="18">
+        <v>10003</v>
+      </c>
+      <c r="G242" s="18">
+        <v>1</v>
+      </c>
+      <c r="H242" s="18">
+        <v>1</v>
+      </c>
+      <c r="I242" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="243" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B243" s="18">
+        <v>500</v>
+      </c>
+      <c r="C243" s="18">
+        <v>8312</v>
+      </c>
+      <c r="D243" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E243" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G243" s="18">
+        <v>24000</v>
+      </c>
+      <c r="H243" s="18">
+        <v>36000</v>
+      </c>
+      <c r="I243" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B244" s="18">
+        <v>501</v>
+      </c>
+      <c r="C244" s="18">
+        <v>8312</v>
+      </c>
+      <c r="D244" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E244" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F244" s="18">
+        <v>10003</v>
+      </c>
+      <c r="G244" s="18">
+        <v>1</v>
+      </c>
+      <c r="H244" s="18">
+        <v>1</v>
+      </c>
+      <c r="I244" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="245" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B245" s="18">
+        <v>502</v>
+      </c>
+      <c r="C245" s="18">
+        <v>8313</v>
+      </c>
+      <c r="D245" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E245" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G245" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H245" s="18">
+        <v>39000</v>
+      </c>
+      <c r="I245" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B246" s="18">
+        <v>503</v>
+      </c>
+      <c r="C246" s="18">
+        <v>8313</v>
+      </c>
+      <c r="D246" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E246" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F246" s="18">
+        <v>10003</v>
+      </c>
+      <c r="G246" s="18">
+        <v>1</v>
+      </c>
+      <c r="H246" s="18">
+        <v>1</v>
+      </c>
+      <c r="I246" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="247" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B247" s="18">
+        <v>504</v>
+      </c>
+      <c r="C247" s="18">
+        <v>8314</v>
+      </c>
+      <c r="D247" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E247" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G247" s="18">
+        <v>28000</v>
+      </c>
+      <c r="H247" s="18">
+        <v>42000</v>
+      </c>
+      <c r="I247" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B248" s="18">
+        <v>505</v>
+      </c>
+      <c r="C248" s="18">
+        <v>8314</v>
+      </c>
+      <c r="D248" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E248" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F248" s="18">
+        <v>10003</v>
+      </c>
+      <c r="G248" s="18">
+        <v>1</v>
+      </c>
+      <c r="H248" s="18">
+        <v>1</v>
+      </c>
+      <c r="I248" s="18">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="249" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B249" s="18">
+        <v>506</v>
+      </c>
+      <c r="C249" s="18">
+        <v>8315</v>
+      </c>
+      <c r="D249" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E249" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G249" s="18">
+        <v>30000</v>
+      </c>
+      <c r="H249" s="18">
+        <v>45000</v>
+      </c>
+      <c r="I249" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B250" s="18">
+        <v>507</v>
+      </c>
+      <c r="C250" s="18">
+        <v>8315</v>
+      </c>
+      <c r="D250" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E250" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F250" s="18">
+        <v>10003</v>
+      </c>
+      <c r="G250" s="18">
+        <v>1</v>
+      </c>
+      <c r="H250" s="18">
+        <v>1</v>
+      </c>
+      <c r="I250" s="18">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="57">
   <si>
     <t>!Enum</t>
   </si>
@@ -692,7 +692,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -745,7 +745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z255"/>
+  <dimension ref="A1:Z264"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="8" customWidth="1"/>
@@ -6988,6 +6988,213 @@
       </c>
       <c r="I255" s="18">
         <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B256" s="18">
+        <v>513</v>
+      </c>
+      <c r="C256" s="18">
+        <v>4101</v>
+      </c>
+      <c r="D256" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E256" s="18">
+        <v>1040200001</v>
+      </c>
+      <c r="G256" s="18">
+        <v>1</v>
+      </c>
+      <c r="H256" s="18">
+        <v>1</v>
+      </c>
+      <c r="I256" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B257" s="18">
+        <v>514</v>
+      </c>
+      <c r="C257" s="18">
+        <v>4102</v>
+      </c>
+      <c r="D257" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E257" s="18">
+        <v>1040200002</v>
+      </c>
+      <c r="G257" s="18">
+        <v>1</v>
+      </c>
+      <c r="H257" s="18">
+        <v>1</v>
+      </c>
+      <c r="I257" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B258" s="18">
+        <v>515</v>
+      </c>
+      <c r="C258" s="18">
+        <v>4103</v>
+      </c>
+      <c r="D258" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E258" s="18">
+        <v>1040200003</v>
+      </c>
+      <c r="G258" s="18">
+        <v>1</v>
+      </c>
+      <c r="H258" s="18">
+        <v>1</v>
+      </c>
+      <c r="I258" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B259" s="18">
+        <v>516</v>
+      </c>
+      <c r="C259" s="18">
+        <v>4104</v>
+      </c>
+      <c r="D259" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E259" s="18">
+        <v>1040200004</v>
+      </c>
+      <c r="G259" s="18">
+        <v>1</v>
+      </c>
+      <c r="H259" s="18">
+        <v>1</v>
+      </c>
+      <c r="I259" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B260" s="18">
+        <v>517</v>
+      </c>
+      <c r="C260" s="18">
+        <v>4105</v>
+      </c>
+      <c r="D260" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E260" s="18">
+        <v>1040200005</v>
+      </c>
+      <c r="G260" s="18">
+        <v>1</v>
+      </c>
+      <c r="H260" s="18">
+        <v>1</v>
+      </c>
+      <c r="I260" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B261" s="18">
+        <v>518</v>
+      </c>
+      <c r="C261" s="18">
+        <v>4106</v>
+      </c>
+      <c r="D261" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E261" s="18">
+        <v>1040200006</v>
+      </c>
+      <c r="G261" s="18">
+        <v>1</v>
+      </c>
+      <c r="H261" s="18">
+        <v>1</v>
+      </c>
+      <c r="I261" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B262" s="18">
+        <v>519</v>
+      </c>
+      <c r="C262" s="18">
+        <v>4201</v>
+      </c>
+      <c r="D262" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E262" s="18">
+        <v>1040100002</v>
+      </c>
+      <c r="G262" s="18">
+        <v>1</v>
+      </c>
+      <c r="H262" s="18">
+        <v>1</v>
+      </c>
+      <c r="I262" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B263" s="18">
+        <v>520</v>
+      </c>
+      <c r="C263" s="18">
+        <v>4202</v>
+      </c>
+      <c r="D263" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E263" s="18">
+        <v>1040100003</v>
+      </c>
+      <c r="G263" s="18">
+        <v>1</v>
+      </c>
+      <c r="H263" s="18">
+        <v>1</v>
+      </c>
+      <c r="I263" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B264" s="18">
+        <v>521</v>
+      </c>
+      <c r="C264" s="18">
+        <v>9101</v>
+      </c>
+      <c r="D264" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E264" s="18">
+        <v>1040200001</v>
+      </c>
+      <c r="G264" s="18">
+        <v>1</v>
+      </c>
+      <c r="H264" s="18">
+        <v>1</v>
+      </c>
+      <c r="I264" s="18">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="55">
   <si>
     <t>!Enum</t>
   </si>
@@ -181,14 +181,6 @@
   </si>
   <si>
     <t>SkillBook</t>
-  </si>
-  <si>
-    <t>Currency</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Currency</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -745,7 +737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z264"/>
+  <dimension ref="A1:Z259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="8" customWidth="1"/>
@@ -876,10 +868,10 @@
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="18">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>4</v>
@@ -887,15 +879,10 @@
       <c r="E4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="18">
-        <v>500</v>
-      </c>
-      <c r="H4" s="18">
-        <v>1500</v>
-      </c>
       <c r="I4">
         <v>1</v>
       </c>
+      <c r="O4" s="12"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="U4" s="18"/>
@@ -908,26 +895,30 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="18">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="18">
-        <v>1020200001</v>
+        <v>3001</v>
+      </c>
+      <c r="F5" s="18">
+        <v>9002</v>
       </c>
       <c r="G5" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
+      <c r="O5" s="12"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="U5" s="18"/>
@@ -939,22 +930,37 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="B6" s="18">
-        <v>3</v>
-      </c>
-      <c r="C6" s="18">
-        <v>2001</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>21</v>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>3001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>1010101001</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="O6" s="12"/>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6">
+        <v>80</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="16"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="U6" s="18"/>
@@ -966,31 +972,34 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="B7" s="18">
-        <v>4</v>
-      </c>
-      <c r="C7" s="18">
-        <v>2001</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="18">
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
         <v>3001</v>
       </c>
-      <c r="F7" s="18">
-        <v>9002</v>
-      </c>
-      <c r="G7" s="18">
-        <v>1</v>
-      </c>
-      <c r="H7" s="18">
+      <c r="D7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1010202001</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
-      <c r="O7" s="12"/>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7">
+        <v>80</v>
+      </c>
+      <c r="O7" s="16"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="U7" s="18"/>
@@ -1003,7 +1012,7 @@
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>3001</v>
@@ -1012,7 +1021,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>1010101001</v>
+        <v>1010203001</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1024,14 +1033,11 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K8">
         <v>80</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
       <c r="O8" s="16"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
@@ -1045,7 +1051,7 @@
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>3001</v>
@@ -1054,7 +1060,7 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <v>1010202001</v>
+        <v>1010306001</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1066,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K9">
         <v>80</v>
@@ -1082,9 +1088,8 @@
       <c r="Z9" s="18"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
       <c r="B10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>3001</v>
@@ -1093,26 +1098,20 @@
         <v>2</v>
       </c>
       <c r="E10">
-        <v>1010203001</v>
+        <v>1020200001</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10">
-        <v>80</v>
-      </c>
-      <c r="O10" s="16"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="5"/>
+      <c r="T10" s="18"/>
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
       <c r="W10" s="18"/>
@@ -1121,37 +1120,28 @@
       <c r="Z10" s="18"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
       <c r="B11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <v>3001</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>1010306001</v>
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>50000</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>50000</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11">
-        <v>80</v>
-      </c>
-      <c r="O11" s="16"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
+      <c r="T11" s="18"/>
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
       <c r="W11" s="18"/>
@@ -1161,28 +1151,26 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <v>3001</v>
       </c>
       <c r="D12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>1020200001</v>
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
-      <c r="O12" s="12"/>
-      <c r="P12" s="5"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
@@ -1193,16 +1181,16 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="D13" t="s">
         <v>2</v>
       </c>
       <c r="E13">
-        <v>1030100001</v>
+        <v>1020200001</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -1213,8 +1201,6 @@
       <c r="I13">
         <v>1</v>
       </c>
-      <c r="O13" s="12"/>
-      <c r="P13" s="5"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
@@ -1225,26 +1211,27 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C14">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="D14" t="s">
         <v>2</v>
       </c>
       <c r="E14">
-        <v>1030100002</v>
+        <v>1020200002</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
+      <c r="O14" s="12"/>
       <c r="T14" s="18"/>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -1255,26 +1242,29 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C15">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="D15" t="s">
         <v>2</v>
       </c>
       <c r="E15">
-        <v>1030200001</v>
+        <v>1020200003</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
       <c r="T15" s="18"/>
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
@@ -1285,10 +1275,10 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -1297,14 +1287,19 @@
         <v>21</v>
       </c>
       <c r="G16">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="H16">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="6"/>
       <c r="T16" s="18"/>
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
@@ -1315,10 +1310,10 @@
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C17">
-        <v>3001</v>
+        <v>4001</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
@@ -1335,6 +1330,7 @@
       <c r="I17">
         <v>1</v>
       </c>
+      <c r="O17" s="15"/>
       <c r="T17" s="18"/>
       <c r="U17" s="18"/>
       <c r="V17" s="18"/>
@@ -1345,26 +1341,27 @@
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C18">
-        <v>3002</v>
+        <v>4002</v>
       </c>
       <c r="D18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>1020200001</v>
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>5000</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>5000</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
+      <c r="O18" s="15"/>
       <c r="T18" s="18"/>
       <c r="U18" s="18"/>
       <c r="V18" s="18"/>
@@ -1375,27 +1372,27 @@
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C19">
-        <v>3002</v>
+        <v>4003</v>
       </c>
       <c r="D19" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>1020200002</v>
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="H19">
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
-      <c r="O19" s="12"/>
+      <c r="O19" s="15"/>
       <c r="T19" s="18"/>
       <c r="U19" s="18"/>
       <c r="V19" s="18"/>
@@ -1406,183 +1403,137 @@
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C20">
-        <v>3002</v>
+        <v>4004</v>
       </c>
       <c r="D20" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>1020200003</v>
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>15000</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>15000</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="18"/>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B21">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C21">
-        <v>3002</v>
+        <v>4005</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G21">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="H21">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="6"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C22">
-        <v>4001</v>
+        <v>4006</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G22">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="H22">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
-      <c r="O22" s="15"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="18"/>
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C23">
-        <v>4002</v>
+        <v>4007</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G23">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="H23">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
-      <c r="O23" s="15"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="18"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="18"/>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C24">
-        <v>4003</v>
+        <v>4008</v>
       </c>
       <c r="D24" t="s">
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G24">
-        <v>10000</v>
+        <v>300000</v>
       </c>
       <c r="H24">
-        <v>10000</v>
+        <v>300000</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="O24" s="15"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="18"/>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C25">
-        <v>4004</v>
+        <v>4009</v>
       </c>
       <c r="D25" t="s">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G25">
-        <v>15000</v>
+        <v>700000</v>
       </c>
       <c r="H25">
-        <v>15000</v>
+        <v>700000</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -1590,22 +1541,22 @@
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C26">
-        <v>4005</v>
+        <v>4010</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G26">
-        <v>20000</v>
+        <v>1200000</v>
       </c>
       <c r="H26">
-        <v>20000</v>
+        <v>1200000</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -1613,45 +1564,55 @@
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C27">
-        <v>4006</v>
+        <v>4011</v>
       </c>
       <c r="D27" t="s">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G27">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H27">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="I27">
         <v>1</v>
       </c>
+      <c r="O27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18"/>
+      <c r="Y27" s="18"/>
+      <c r="Z27" s="18"/>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C28">
-        <v>4007</v>
+        <v>4012</v>
       </c>
       <c r="D28" t="s">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G28">
-        <v>50000</v>
+        <v>12000</v>
       </c>
       <c r="H28">
-        <v>50000</v>
+        <v>12000</v>
       </c>
       <c r="I28">
         <v>1</v>
@@ -1659,22 +1620,22 @@
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C29">
-        <v>4008</v>
+        <v>4013</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G29">
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="H29">
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -1682,22 +1643,22 @@
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C30">
-        <v>4009</v>
+        <v>4014</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G30">
-        <v>700000</v>
+        <v>200000</v>
       </c>
       <c r="H30">
-        <v>700000</v>
+        <v>200000</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -1705,22 +1666,22 @@
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C31">
-        <v>4010</v>
+        <v>4015</v>
       </c>
       <c r="D31" t="s">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G31">
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H31">
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -1728,55 +1689,51 @@
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C32">
-        <v>4011</v>
+        <v>5001</v>
       </c>
       <c r="D32" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>3001</v>
+      </c>
+      <c r="F32">
+        <v>40001</v>
       </c>
       <c r="G32">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
-      <c r="O32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="18"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="18"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C33">
-        <v>4012</v>
+        <v>5002</v>
       </c>
       <c r="D33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>3001</v>
+      </c>
+      <c r="F33">
+        <v>40002</v>
       </c>
       <c r="G33">
-        <v>12000</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>12000</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>1</v>
@@ -1784,22 +1741,25 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C34">
-        <v>4013</v>
+        <v>5003</v>
       </c>
       <c r="D34" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>3001</v>
+      </c>
+      <c r="F34">
+        <v>40003</v>
       </c>
       <c r="G34">
-        <v>80000</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>80000</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -1807,22 +1767,22 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C35">
-        <v>4014</v>
+        <v>6001</v>
       </c>
       <c r="D35" t="s">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G35">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="H35">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -1830,22 +1790,22 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C36">
-        <v>4015</v>
+        <v>6002</v>
       </c>
       <c r="D36" t="s">
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G36">
-        <v>600000</v>
+        <v>50</v>
       </c>
       <c r="H36">
-        <v>600000</v>
+        <v>50</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -1853,22 +1813,22 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C37">
-        <v>4016</v>
+        <v>6003</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="E37" t="s">
         <v>21</v>
       </c>
       <c r="G37">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="H37">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -1876,22 +1836,22 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C38">
-        <v>4017</v>
+        <v>6004</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G38">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H38">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -1899,25 +1859,22 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C39">
-        <v>5001</v>
+        <v>6005</v>
       </c>
       <c r="D39" t="s">
-        <v>3</v>
-      </c>
-      <c r="E39">
-        <v>3001</v>
-      </c>
-      <c r="F39">
-        <v>40001</v>
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
+        <v>26</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -1925,25 +1882,22 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C40">
-        <v>5002</v>
+        <v>6006</v>
       </c>
       <c r="D40" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40">
-        <v>3001</v>
-      </c>
-      <c r="F40">
-        <v>40002</v>
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -1951,25 +1905,22 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C41">
-        <v>5003</v>
+        <v>6007</v>
       </c>
       <c r="D41" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41">
-        <v>3001</v>
-      </c>
-      <c r="F41">
-        <v>40003</v>
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>26</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -1977,10 +1928,10 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C42">
-        <v>6001</v>
+        <v>6008</v>
       </c>
       <c r="D42" t="s">
         <v>4</v>
@@ -1989,10 +1940,10 @@
         <v>21</v>
       </c>
       <c r="G42">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="H42">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="I42">
         <v>1</v>
@@ -2000,22 +1951,22 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C43">
-        <v>6002</v>
+        <v>6009</v>
       </c>
       <c r="D43" t="s">
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G43">
-        <v>50</v>
+        <v>12000</v>
       </c>
       <c r="H43">
-        <v>50</v>
+        <v>12000</v>
       </c>
       <c r="I43">
         <v>1</v>
@@ -2023,22 +1974,22 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C44">
-        <v>6003</v>
+        <v>6010</v>
       </c>
       <c r="D44" t="s">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G44">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="H44">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -2046,10 +1997,10 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="C45">
-        <v>6004</v>
+        <v>7101</v>
       </c>
       <c r="D45" t="s">
         <v>4</v>
@@ -2058,10 +2009,10 @@
         <v>21</v>
       </c>
       <c r="G45">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H45">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="I45">
         <v>1</v>
@@ -2069,22 +2020,22 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="C46">
-        <v>6005</v>
+        <v>7102</v>
       </c>
       <c r="D46" t="s">
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H46">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -2092,22 +2043,22 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="C47">
-        <v>6006</v>
+        <v>7103</v>
       </c>
       <c r="D47" t="s">
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G47">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="H47">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="I47">
         <v>1</v>
@@ -2115,22 +2066,22 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C48">
-        <v>6007</v>
+        <v>7104</v>
       </c>
       <c r="D48" t="s">
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G48">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="H48">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -2138,22 +2089,22 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="C49">
-        <v>6008</v>
+        <v>7105</v>
       </c>
       <c r="D49" t="s">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G49">
-        <v>8000</v>
+        <v>10</v>
       </c>
       <c r="H49">
-        <v>8000</v>
+        <v>10</v>
       </c>
       <c r="I49">
         <v>1</v>
@@ -2161,22 +2112,22 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C50">
-        <v>6009</v>
+        <v>7106</v>
       </c>
       <c r="D50" t="s">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G50">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="H50">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -2184,22 +2135,22 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="C51">
-        <v>6010</v>
+        <v>7107</v>
       </c>
       <c r="D51" t="s">
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G51">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="I51">
         <v>1</v>
@@ -2207,10 +2158,10 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C52">
-        <v>7101</v>
+        <v>7201</v>
       </c>
       <c r="D52" t="s">
         <v>4</v>
@@ -2219,10 +2170,10 @@
         <v>21</v>
       </c>
       <c r="G52">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H52">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I52">
         <v>1</v>
@@ -2230,10 +2181,10 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C53">
-        <v>7102</v>
+        <v>7202</v>
       </c>
       <c r="D53" t="s">
         <v>4</v>
@@ -2242,10 +2193,10 @@
         <v>28</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -2253,22 +2204,22 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C54">
-        <v>7103</v>
+        <v>7203</v>
       </c>
       <c r="D54" t="s">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G54">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="H54">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="I54">
         <v>1</v>
@@ -2276,10 +2227,10 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C55">
-        <v>7104</v>
+        <v>7204</v>
       </c>
       <c r="D55" t="s">
         <v>4</v>
@@ -2288,10 +2239,10 @@
         <v>29</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -2299,22 +2250,22 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C56">
-        <v>7105</v>
+        <v>7205</v>
       </c>
       <c r="D56" t="s">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G56">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H56">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I56">
         <v>1</v>
@@ -2322,16 +2273,16 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C57">
-        <v>7106</v>
+        <v>7206</v>
       </c>
       <c r="D57" t="s">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G57">
         <v>3000</v>
@@ -2345,16 +2296,16 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C58">
-        <v>7107</v>
+        <v>7207</v>
       </c>
       <c r="D58" t="s">
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G58">
         <v>3</v>
@@ -2368,22 +2319,22 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C59">
-        <v>7201</v>
+        <v>7208</v>
       </c>
       <c r="D59" t="s">
         <v>4</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G59">
-        <v>2000</v>
+        <v>5</v>
       </c>
       <c r="H59">
-        <v>2000</v>
+        <v>5</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -2391,22 +2342,22 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C60">
-        <v>7202</v>
+        <v>7209</v>
       </c>
       <c r="D60" t="s">
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -2414,22 +2365,22 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C61">
-        <v>7203</v>
+        <v>7210</v>
       </c>
       <c r="D61" t="s">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G61">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H61">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="I61">
         <v>1</v>
@@ -2437,22 +2388,22 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C62">
-        <v>7204</v>
+        <v>7211</v>
       </c>
       <c r="D62" t="s">
         <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>4000</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>4000</v>
       </c>
       <c r="I62">
         <v>1</v>
@@ -2460,22 +2411,22 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C63">
-        <v>7205</v>
+        <v>7212</v>
       </c>
       <c r="D63" t="s">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G63">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H63">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I63">
         <v>1</v>
@@ -2483,22 +2434,22 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C64">
-        <v>7206</v>
+        <v>7213</v>
       </c>
       <c r="D64" t="s">
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G64">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H64">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I64">
         <v>1</v>
@@ -2506,16 +2457,16 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C65">
-        <v>7207</v>
+        <v>7214</v>
       </c>
       <c r="D65" t="s">
         <v>4</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -2529,22 +2480,22 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C66">
-        <v>7208</v>
+        <v>7215</v>
       </c>
       <c r="D66" t="s">
         <v>4</v>
       </c>
       <c r="E66" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I66">
         <v>1</v>
@@ -2552,22 +2503,22 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C67">
-        <v>7209</v>
+        <v>7216</v>
       </c>
       <c r="D67" t="s">
         <v>4</v>
       </c>
       <c r="E67" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G67">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="H67">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="I67">
         <v>1</v>
@@ -2575,22 +2526,22 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C68">
-        <v>7210</v>
+        <v>7217</v>
       </c>
       <c r="D68" t="s">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G68">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="H68">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="I68">
         <v>1</v>
@@ -2598,22 +2549,22 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C69">
-        <v>7211</v>
+        <v>7218</v>
       </c>
       <c r="D69" t="s">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G69">
-        <v>4000</v>
+        <v>10</v>
       </c>
       <c r="H69">
-        <v>4000</v>
+        <v>10</v>
       </c>
       <c r="I69">
         <v>1</v>
@@ -2621,16 +2572,16 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C70">
-        <v>7212</v>
+        <v>7219</v>
       </c>
       <c r="D70" t="s">
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G70">
         <v>5</v>
@@ -2644,22 +2595,22 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C71">
-        <v>7213</v>
+        <v>7220</v>
       </c>
       <c r="D71" t="s">
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G71">
-        <v>2000</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>2000</v>
+        <v>3</v>
       </c>
       <c r="I71">
         <v>1</v>
@@ -2667,22 +2618,22 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C72">
-        <v>7214</v>
+        <v>7221</v>
       </c>
       <c r="D72" t="s">
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>6000</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>6000</v>
       </c>
       <c r="I72">
         <v>1</v>
@@ -2690,22 +2641,22 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C73">
-        <v>7215</v>
+        <v>7222</v>
       </c>
       <c r="D73" t="s">
         <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -2713,22 +2664,22 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C74">
-        <v>7216</v>
+        <v>7223</v>
       </c>
       <c r="D74" t="s">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G74">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H74">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I74">
         <v>1</v>
@@ -2736,22 +2687,22 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C75">
-        <v>7217</v>
+        <v>7224</v>
       </c>
       <c r="D75" t="s">
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G75">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H75">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -2759,22 +2710,22 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C76">
-        <v>7218</v>
+        <v>7225</v>
       </c>
       <c r="D76" t="s">
         <v>4</v>
       </c>
       <c r="E76" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G76">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="H76">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="I76">
         <v>1</v>
@@ -2782,22 +2733,22 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C77">
-        <v>7219</v>
+        <v>7226</v>
       </c>
       <c r="D77" t="s">
         <v>4</v>
       </c>
       <c r="E77" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>8000</v>
       </c>
       <c r="H77">
-        <v>5</v>
+        <v>8000</v>
       </c>
       <c r="I77">
         <v>1</v>
@@ -2805,22 +2756,22 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C78">
-        <v>7220</v>
+        <v>7227</v>
       </c>
       <c r="D78" t="s">
         <v>4</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I78">
         <v>1</v>
@@ -2828,22 +2779,22 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C79">
-        <v>7221</v>
+        <v>7228</v>
       </c>
       <c r="D79" t="s">
         <v>4</v>
       </c>
       <c r="E79" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G79">
-        <v>6000</v>
+        <v>15</v>
       </c>
       <c r="H79">
-        <v>6000</v>
+        <v>15</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -2851,22 +2802,22 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C80">
-        <v>7222</v>
+        <v>7229</v>
       </c>
       <c r="D80" t="s">
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G80">
-        <v>10</v>
+        <v>5000</v>
       </c>
       <c r="H80">
-        <v>10</v>
+        <v>5000</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -2874,22 +2825,22 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C81">
-        <v>7223</v>
+        <v>7230</v>
       </c>
       <c r="D81" t="s">
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G81">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H81">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -2897,22 +2848,22 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="C82">
-        <v>7224</v>
+        <v>9001</v>
       </c>
       <c r="D82" t="s">
         <v>4</v>
       </c>
       <c r="E82" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G82">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="H82">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -2920,68 +2871,71 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="C83">
-        <v>7225</v>
+        <v>9001</v>
       </c>
       <c r="D83" t="s">
         <v>4</v>
       </c>
       <c r="E83" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G83">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H83">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="C84">
-        <v>7226</v>
+        <v>9001</v>
       </c>
       <c r="D84" t="s">
-        <v>4</v>
-      </c>
-      <c r="E84" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="E84">
+        <v>3001</v>
+      </c>
+      <c r="F84">
+        <v>10001</v>
       </c>
       <c r="G84">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="H84">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="I84">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
-        <v>136</v>
+        <v>300</v>
       </c>
       <c r="C85">
-        <v>7227</v>
+        <v>7501</v>
       </c>
       <c r="D85" t="s">
         <v>4</v>
       </c>
       <c r="E85" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G85">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="H85">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -2989,22 +2943,22 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86">
-        <v>137</v>
+        <v>301</v>
       </c>
       <c r="C86">
-        <v>7228</v>
+        <v>7502</v>
       </c>
       <c r="D86" t="s">
         <v>4</v>
       </c>
       <c r="E86" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G86">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H86">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I86">
         <v>1</v>
@@ -3012,22 +2966,22 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87">
-        <v>138</v>
+        <v>302</v>
       </c>
       <c r="C87">
-        <v>7229</v>
+        <v>7503</v>
       </c>
       <c r="D87" t="s">
         <v>4</v>
       </c>
       <c r="E87" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G87">
-        <v>5000</v>
+        <v>3</v>
       </c>
       <c r="H87">
-        <v>5000</v>
+        <v>3</v>
       </c>
       <c r="I87">
         <v>1</v>
@@ -3035,16 +2989,16 @@
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88">
-        <v>139</v>
+        <v>303</v>
       </c>
       <c r="C88">
-        <v>7230</v>
+        <v>7504</v>
       </c>
       <c r="D88" t="s">
         <v>4</v>
       </c>
       <c r="E88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G88">
         <v>5</v>
@@ -3058,22 +3012,22 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89">
-        <v>200</v>
+        <v>304</v>
       </c>
       <c r="C89">
-        <v>9001</v>
+        <v>7505</v>
       </c>
       <c r="D89" t="s">
         <v>4</v>
       </c>
       <c r="E89" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G89">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H89">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="I89">
         <v>1</v>
@@ -3081,94 +3035,91 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90">
-        <v>201</v>
+        <v>305</v>
       </c>
       <c r="C90">
-        <v>9001</v>
+        <v>7506</v>
       </c>
       <c r="D90" t="s">
         <v>4</v>
       </c>
       <c r="E90" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="H90">
-        <v>2</v>
+        <v>3000</v>
       </c>
       <c r="I90">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91">
-        <v>202</v>
+        <v>306</v>
       </c>
       <c r="C91">
-        <v>9001</v>
+        <v>7507</v>
       </c>
       <c r="D91" t="s">
-        <v>2</v>
-      </c>
-      <c r="E91">
-        <v>1030100001</v>
+        <v>4</v>
+      </c>
+      <c r="E91" t="s">
+        <v>28</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="C92">
-        <v>9001</v>
+        <v>7508</v>
       </c>
       <c r="D92" t="s">
-        <v>3</v>
-      </c>
-      <c r="E92">
-        <v>3001</v>
-      </c>
-      <c r="F92">
-        <v>10001</v>
+        <v>4</v>
+      </c>
+      <c r="E92" t="s">
+        <v>29</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I92">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C93">
-        <v>7501</v>
+        <v>7509</v>
       </c>
       <c r="D93" t="s">
         <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G93">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H93">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I93">
         <v>1</v>
@@ -3176,22 +3127,22 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C94">
-        <v>7502</v>
+        <v>7510</v>
       </c>
       <c r="D94" t="s">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H94">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I94">
         <v>1</v>
@@ -3199,22 +3150,22 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C95">
-        <v>7503</v>
+        <v>7511</v>
       </c>
       <c r="D95" t="s">
         <v>4</v>
       </c>
       <c r="E95" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G95">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="H95">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I95">
         <v>1</v>
@@ -3222,22 +3173,22 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C96">
-        <v>7504</v>
+        <v>7512</v>
       </c>
       <c r="D96" t="s">
         <v>4</v>
       </c>
       <c r="E96" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H96">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I96">
         <v>1</v>
@@ -3245,22 +3196,22 @@
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C97">
-        <v>7505</v>
+        <v>7513</v>
       </c>
       <c r="D97" t="s">
         <v>4</v>
       </c>
       <c r="E97" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G97">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H97">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I97">
         <v>1</v>
@@ -3268,22 +3219,22 @@
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C98">
-        <v>7506</v>
+        <v>7514</v>
       </c>
       <c r="D98" t="s">
         <v>4</v>
       </c>
       <c r="E98" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G98">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H98">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I98">
         <v>1</v>
@@ -3291,22 +3242,22 @@
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C99">
-        <v>7507</v>
+        <v>7515</v>
       </c>
       <c r="D99" t="s">
         <v>4</v>
       </c>
       <c r="E99" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G99">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H99">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I99">
         <v>1</v>
@@ -3314,22 +3265,22 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C100">
-        <v>7508</v>
+        <v>7516</v>
       </c>
       <c r="D100" t="s">
         <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G100">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="H100">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -3337,22 +3288,22 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C101">
-        <v>7509</v>
+        <v>7517</v>
       </c>
       <c r="D101" t="s">
         <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H101">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I101">
         <v>1</v>
@@ -3360,22 +3311,22 @@
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C102">
-        <v>7510</v>
+        <v>7518</v>
       </c>
       <c r="D102" t="s">
         <v>4</v>
       </c>
       <c r="E102" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G102">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H102">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I102">
         <v>1</v>
@@ -3383,22 +3334,22 @@
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C103">
-        <v>7511</v>
+        <v>7519</v>
       </c>
       <c r="D103" t="s">
         <v>4</v>
       </c>
       <c r="E103" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G103">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H103">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I103">
         <v>1</v>
@@ -3406,22 +3357,22 @@
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B104">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C104">
-        <v>7512</v>
+        <v>7520</v>
       </c>
       <c r="D104" t="s">
         <v>4</v>
       </c>
       <c r="E104" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G104">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H104">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I104">
         <v>1</v>
@@ -3429,22 +3380,22 @@
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B105">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C105">
-        <v>7513</v>
+        <v>7521</v>
       </c>
       <c r="D105" t="s">
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G105">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="H105">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I105">
         <v>1</v>
@@ -3452,22 +3403,22 @@
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B106">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C106">
-        <v>7514</v>
+        <v>7522</v>
       </c>
       <c r="D106" t="s">
         <v>4</v>
       </c>
       <c r="E106" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I106">
         <v>1</v>
@@ -3475,22 +3426,22 @@
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B107">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C107">
-        <v>7515</v>
+        <v>7523</v>
       </c>
       <c r="D107" t="s">
         <v>4</v>
       </c>
       <c r="E107" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G107">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H107">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I107">
         <v>1</v>
@@ -3498,22 +3449,22 @@
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C108">
-        <v>7516</v>
+        <v>7524</v>
       </c>
       <c r="D108" t="s">
         <v>4</v>
       </c>
       <c r="E108" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G108">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H108">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I108">
         <v>1</v>
@@ -3521,22 +3472,22 @@
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B109">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C109">
-        <v>7517</v>
+        <v>7525</v>
       </c>
       <c r="D109" t="s">
         <v>4</v>
       </c>
       <c r="E109" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G109">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H109">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I109">
         <v>1</v>
@@ -3544,22 +3495,22 @@
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B110">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C110">
-        <v>7518</v>
+        <v>7526</v>
       </c>
       <c r="D110" t="s">
         <v>4</v>
       </c>
       <c r="E110" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G110">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="H110">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I110">
         <v>1</v>
@@ -3567,22 +3518,22 @@
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C111">
-        <v>7519</v>
+        <v>7527</v>
       </c>
       <c r="D111" t="s">
         <v>4</v>
       </c>
       <c r="E111" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I111">
         <v>1</v>
@@ -3590,22 +3541,22 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C112">
-        <v>7520</v>
+        <v>7528</v>
       </c>
       <c r="D112" t="s">
         <v>4</v>
       </c>
       <c r="E112" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G112">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H112">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I112">
         <v>1</v>
@@ -3613,22 +3564,22 @@
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C113">
-        <v>7521</v>
+        <v>7529</v>
       </c>
       <c r="D113" t="s">
         <v>4</v>
       </c>
       <c r="E113" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G113">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H113">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I113">
         <v>1</v>
@@ -3636,22 +3587,22 @@
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B114">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C114">
-        <v>7522</v>
+        <v>7530</v>
       </c>
       <c r="D114" t="s">
         <v>4</v>
       </c>
       <c r="E114" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G114">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H114">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I114">
         <v>1</v>
@@ -3659,22 +3610,22 @@
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B115">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C115">
-        <v>7523</v>
+        <v>7531</v>
       </c>
       <c r="D115" t="s">
         <v>4</v>
       </c>
       <c r="E115" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G115">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="H115">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I115">
         <v>1</v>
@@ -3682,22 +3633,22 @@
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B116">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C116">
-        <v>7524</v>
+        <v>7532</v>
       </c>
       <c r="D116" t="s">
         <v>4</v>
       </c>
       <c r="E116" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G116">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H116">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I116">
         <v>1</v>
@@ -3705,22 +3656,22 @@
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B117">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C117">
-        <v>7525</v>
+        <v>7533</v>
       </c>
       <c r="D117" t="s">
         <v>4</v>
       </c>
       <c r="E117" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G117">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H117">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I117">
         <v>1</v>
@@ -3728,22 +3679,22 @@
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B118">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C118">
-        <v>7526</v>
+        <v>7534</v>
       </c>
       <c r="D118" t="s">
         <v>4</v>
       </c>
       <c r="E118" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G118">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H118">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I118">
         <v>1</v>
@@ -3751,22 +3702,22 @@
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B119">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C119">
-        <v>7527</v>
+        <v>7535</v>
       </c>
       <c r="D119" t="s">
         <v>4</v>
       </c>
       <c r="E119" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G119">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H119">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I119">
         <v>1</v>
@@ -3774,22 +3725,22 @@
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B120">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C120">
-        <v>7528</v>
+        <v>7536</v>
       </c>
       <c r="D120" t="s">
         <v>4</v>
       </c>
       <c r="E120" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G120">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="H120">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I120">
         <v>1</v>
@@ -3797,22 +3748,22 @@
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B121">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C121">
-        <v>7529</v>
+        <v>7537</v>
       </c>
       <c r="D121" t="s">
         <v>4</v>
       </c>
       <c r="E121" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G121">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H121">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I121">
         <v>1</v>
@@ -3820,22 +3771,22 @@
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B122">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C122">
-        <v>7530</v>
+        <v>7538</v>
       </c>
       <c r="D122" t="s">
         <v>4</v>
       </c>
       <c r="E122" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G122">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H122">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I122">
         <v>1</v>
@@ -3843,22 +3794,22 @@
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B123">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C123">
-        <v>7531</v>
+        <v>7539</v>
       </c>
       <c r="D123" t="s">
         <v>4</v>
       </c>
       <c r="E123" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G123">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H123">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I123">
         <v>1</v>
@@ -3866,22 +3817,22 @@
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B124">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C124">
-        <v>7532</v>
+        <v>7540</v>
       </c>
       <c r="D124" t="s">
         <v>4</v>
       </c>
       <c r="E124" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G124">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H124">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I124">
         <v>1</v>
@@ -3889,22 +3840,22 @@
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B125">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C125">
-        <v>7533</v>
+        <v>7541</v>
       </c>
       <c r="D125" t="s">
         <v>4</v>
       </c>
       <c r="E125" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G125">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="H125">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I125">
         <v>1</v>
@@ -3912,22 +3863,22 @@
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B126">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C126">
-        <v>7534</v>
+        <v>7542</v>
       </c>
       <c r="D126" t="s">
         <v>4</v>
       </c>
       <c r="E126" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G126">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H126">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I126">
         <v>1</v>
@@ -3935,22 +3886,22 @@
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B127">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C127">
-        <v>7535</v>
+        <v>7543</v>
       </c>
       <c r="D127" t="s">
         <v>4</v>
       </c>
       <c r="E127" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G127">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H127">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I127">
         <v>1</v>
@@ -3958,22 +3909,22 @@
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B128">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C128">
-        <v>7536</v>
+        <v>7544</v>
       </c>
       <c r="D128" t="s">
         <v>4</v>
       </c>
       <c r="E128" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G128">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H128">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I128">
         <v>1</v>
@@ -3981,22 +3932,22 @@
     </row>
     <row r="129" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B129">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C129">
-        <v>7537</v>
+        <v>7545</v>
       </c>
       <c r="D129" t="s">
         <v>4</v>
       </c>
       <c r="E129" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G129">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H129">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I129">
         <v>1</v>
@@ -4004,22 +3955,22 @@
     </row>
     <row r="130" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B130">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C130">
-        <v>7538</v>
+        <v>7546</v>
       </c>
       <c r="D130" t="s">
         <v>4</v>
       </c>
       <c r="E130" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G130">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="H130">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I130">
         <v>1</v>
@@ -4027,22 +3978,22 @@
     </row>
     <row r="131" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B131">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C131">
-        <v>7539</v>
+        <v>7547</v>
       </c>
       <c r="D131" t="s">
         <v>4</v>
       </c>
       <c r="E131" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G131">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H131">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I131">
         <v>1</v>
@@ -4050,22 +4001,22 @@
     </row>
     <row r="132" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B132">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C132">
-        <v>7540</v>
+        <v>7548</v>
       </c>
       <c r="D132" t="s">
         <v>4</v>
       </c>
       <c r="E132" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G132">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H132">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I132">
         <v>1</v>
@@ -4073,22 +4024,22 @@
     </row>
     <row r="133" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B133">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C133">
-        <v>7541</v>
+        <v>7549</v>
       </c>
       <c r="D133" t="s">
         <v>4</v>
       </c>
       <c r="E133" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G133">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="H133">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="I133">
         <v>1</v>
@@ -4096,22 +4047,22 @@
     </row>
     <row r="134" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B134">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C134">
-        <v>7542</v>
+        <v>7550</v>
       </c>
       <c r="D134" t="s">
         <v>4</v>
       </c>
       <c r="E134" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G134">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H134">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I134">
         <v>1</v>
@@ -4119,22 +4070,22 @@
     </row>
     <row r="135" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B135">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="C135">
-        <v>7543</v>
+        <v>7601</v>
       </c>
       <c r="D135" t="s">
         <v>4</v>
       </c>
       <c r="E135" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G135">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="H135">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="I135">
         <v>1</v>
@@ -4142,16 +4093,16 @@
     </row>
     <row r="136" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B136">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="C136">
-        <v>7544</v>
+        <v>7602</v>
       </c>
       <c r="D136" t="s">
         <v>4</v>
       </c>
       <c r="E136" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G136">
         <v>5</v>
@@ -4165,22 +4116,22 @@
     </row>
     <row r="137" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B137">
-        <v>344</v>
+        <v>402</v>
       </c>
       <c r="C137">
-        <v>7545</v>
+        <v>7603</v>
       </c>
       <c r="D137" t="s">
         <v>4</v>
       </c>
       <c r="E137" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G137">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H137">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I137">
         <v>1</v>
@@ -4188,22 +4139,22 @@
     </row>
     <row r="138" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B138">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C138">
-        <v>7546</v>
+        <v>7604</v>
       </c>
       <c r="D138" t="s">
         <v>4</v>
       </c>
       <c r="E138" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G138">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="H138">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="I138">
         <v>1</v>
@@ -4211,22 +4162,22 @@
     </row>
     <row r="139" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B139">
-        <v>346</v>
+        <v>404</v>
       </c>
       <c r="C139">
-        <v>7547</v>
+        <v>7605</v>
       </c>
       <c r="D139" t="s">
         <v>4</v>
       </c>
       <c r="E139" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G139">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="H139">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="I139">
         <v>1</v>
@@ -4234,22 +4185,22 @@
     </row>
     <row r="140" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B140">
-        <v>347</v>
+        <v>405</v>
       </c>
       <c r="C140">
-        <v>7548</v>
+        <v>7606</v>
       </c>
       <c r="D140" t="s">
         <v>4</v>
       </c>
       <c r="E140" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G140">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="H140">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="I140">
         <v>1</v>
@@ -4257,16 +4208,16 @@
     </row>
     <row r="141" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B141">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="C141">
-        <v>7549</v>
+        <v>7607</v>
       </c>
       <c r="D141" t="s">
         <v>4</v>
       </c>
       <c r="E141" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G141">
         <v>5</v>
@@ -4280,22 +4231,22 @@
     </row>
     <row r="142" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B142">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="C142">
-        <v>7550</v>
+        <v>7608</v>
       </c>
       <c r="D142" t="s">
         <v>4</v>
       </c>
       <c r="E142" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G142">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H142">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I142">
         <v>1</v>
@@ -4303,22 +4254,22 @@
     </row>
     <row r="143" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B143">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C143">
-        <v>7601</v>
+        <v>7609</v>
       </c>
       <c r="D143" t="s">
         <v>4</v>
       </c>
       <c r="E143" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G143">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H143">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -4326,22 +4277,22 @@
     </row>
     <row r="144" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B144">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C144">
-        <v>7602</v>
+        <v>7610</v>
       </c>
       <c r="D144" t="s">
         <v>4</v>
       </c>
       <c r="E144" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G144">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H144">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -4349,22 +4300,22 @@
     </row>
     <row r="145" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B145">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C145">
-        <v>7603</v>
+        <v>7611</v>
       </c>
       <c r="D145" t="s">
         <v>4</v>
       </c>
       <c r="E145" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G145">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="H145">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -4372,22 +4323,22 @@
     </row>
     <row r="146" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B146">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C146">
-        <v>7604</v>
+        <v>7612</v>
       </c>
       <c r="D146" t="s">
         <v>4</v>
       </c>
       <c r="E146" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G146">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H146">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -4395,22 +4346,22 @@
     </row>
     <row r="147" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B147">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C147">
-        <v>7605</v>
+        <v>7613</v>
       </c>
       <c r="D147" t="s">
         <v>4</v>
       </c>
       <c r="E147" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G147">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="H147">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -4418,22 +4369,22 @@
     </row>
     <row r="148" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B148">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C148">
-        <v>7606</v>
+        <v>7614</v>
       </c>
       <c r="D148" t="s">
         <v>4</v>
       </c>
       <c r="E148" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G148">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H148">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -4441,22 +4392,22 @@
     </row>
     <row r="149" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B149">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C149">
-        <v>7607</v>
+        <v>7615</v>
       </c>
       <c r="D149" t="s">
         <v>4</v>
       </c>
       <c r="E149" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G149">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="H149">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="I149">
         <v>1</v>
@@ -4464,22 +4415,22 @@
     </row>
     <row r="150" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B150">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C150">
-        <v>7608</v>
+        <v>7616</v>
       </c>
       <c r="D150" t="s">
         <v>4</v>
       </c>
       <c r="E150" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G150">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="H150">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I150">
         <v>1</v>
@@ -4487,22 +4438,22 @@
     </row>
     <row r="151" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B151">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C151">
-        <v>7609</v>
+        <v>7617</v>
       </c>
       <c r="D151" t="s">
         <v>4</v>
       </c>
       <c r="E151" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G151">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H151">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I151">
         <v>1</v>
@@ -4510,22 +4461,22 @@
     </row>
     <row r="152" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B152">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C152">
-        <v>7610</v>
+        <v>7618</v>
       </c>
       <c r="D152" t="s">
         <v>4</v>
       </c>
       <c r="E152" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G152">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H152">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I152">
         <v>1</v>
@@ -4533,22 +4484,22 @@
     </row>
     <row r="153" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B153">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C153">
-        <v>7611</v>
+        <v>7619</v>
       </c>
       <c r="D153" t="s">
         <v>4</v>
       </c>
       <c r="E153" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G153">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H153">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I153">
         <v>1</v>
@@ -4556,22 +4507,22 @@
     </row>
     <row r="154" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B154">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C154">
-        <v>7612</v>
+        <v>7620</v>
       </c>
       <c r="D154" t="s">
         <v>4</v>
       </c>
       <c r="E154" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G154">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H154">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I154">
         <v>1</v>
@@ -4579,22 +4530,22 @@
     </row>
     <row r="155" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B155">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C155">
-        <v>7613</v>
+        <v>7621</v>
       </c>
       <c r="D155" t="s">
         <v>4</v>
       </c>
       <c r="E155" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G155">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="H155">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I155">
         <v>1</v>
@@ -4602,22 +4553,22 @@
     </row>
     <row r="156" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B156">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C156">
-        <v>7614</v>
+        <v>7622</v>
       </c>
       <c r="D156" t="s">
         <v>4</v>
       </c>
       <c r="E156" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G156">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H156">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I156">
         <v>1</v>
@@ -4625,22 +4576,22 @@
     </row>
     <row r="157" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B157">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C157">
-        <v>7615</v>
+        <v>7623</v>
       </c>
       <c r="D157" t="s">
         <v>4</v>
       </c>
       <c r="E157" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G157">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="H157">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="I157">
         <v>1</v>
@@ -4648,22 +4599,22 @@
     </row>
     <row r="158" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B158">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C158">
-        <v>7616</v>
+        <v>7624</v>
       </c>
       <c r="D158" t="s">
         <v>4</v>
       </c>
       <c r="E158" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G158">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H158">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I158">
         <v>1</v>
@@ -4671,22 +4622,22 @@
     </row>
     <row r="159" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B159">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C159">
-        <v>7617</v>
+        <v>7625</v>
       </c>
       <c r="D159" t="s">
         <v>4</v>
       </c>
       <c r="E159" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G159">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="H159">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="I159">
         <v>1</v>
@@ -4694,22 +4645,22 @@
     </row>
     <row r="160" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B160">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C160">
-        <v>7618</v>
+        <v>7626</v>
       </c>
       <c r="D160" t="s">
         <v>4</v>
       </c>
       <c r="E160" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G160">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="H160">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I160">
         <v>1</v>
@@ -4717,22 +4668,22 @@
     </row>
     <row r="161" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B161">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C161">
-        <v>7619</v>
+        <v>7627</v>
       </c>
       <c r="D161" t="s">
         <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G161">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H161">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I161">
         <v>1</v>
@@ -4740,22 +4691,22 @@
     </row>
     <row r="162" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B162">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C162">
-        <v>7620</v>
+        <v>7628</v>
       </c>
       <c r="D162" t="s">
         <v>4</v>
       </c>
       <c r="E162" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G162">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H162">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I162">
         <v>1</v>
@@ -4763,22 +4714,22 @@
     </row>
     <row r="163" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B163">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C163">
-        <v>7621</v>
+        <v>7629</v>
       </c>
       <c r="D163" t="s">
         <v>4</v>
       </c>
       <c r="E163" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G163">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H163">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I163">
         <v>1</v>
@@ -4786,22 +4737,22 @@
     </row>
     <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C164">
-        <v>7622</v>
+        <v>7630</v>
       </c>
       <c r="D164" t="s">
         <v>4</v>
       </c>
       <c r="E164" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G164">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H164">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I164">
         <v>1</v>
@@ -4809,22 +4760,22 @@
     </row>
     <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B165">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C165">
-        <v>7623</v>
+        <v>7631</v>
       </c>
       <c r="D165" t="s">
         <v>4</v>
       </c>
       <c r="E165" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G165">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="H165">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I165">
         <v>1</v>
@@ -4832,22 +4783,22 @@
     </row>
     <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B166">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C166">
-        <v>7624</v>
+        <v>7632</v>
       </c>
       <c r="D166" t="s">
         <v>4</v>
       </c>
       <c r="E166" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G166">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H166">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I166">
         <v>1</v>
@@ -4855,22 +4806,22 @@
     </row>
     <row r="167" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B167">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C167">
-        <v>7625</v>
+        <v>7633</v>
       </c>
       <c r="D167" t="s">
         <v>4</v>
       </c>
       <c r="E167" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G167">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="H167">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="I167">
         <v>1</v>
@@ -4878,22 +4829,22 @@
     </row>
     <row r="168" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B168">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C168">
-        <v>7626</v>
+        <v>7634</v>
       </c>
       <c r="D168" t="s">
         <v>4</v>
       </c>
       <c r="E168" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G168">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H168">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I168">
         <v>1</v>
@@ -4901,22 +4852,22 @@
     </row>
     <row r="169" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B169">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C169">
-        <v>7627</v>
+        <v>7635</v>
       </c>
       <c r="D169" t="s">
         <v>4</v>
       </c>
       <c r="E169" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G169">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="H169">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="I169">
         <v>1</v>
@@ -4924,22 +4875,22 @@
     </row>
     <row r="170" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B170">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C170">
-        <v>7628</v>
+        <v>7636</v>
       </c>
       <c r="D170" t="s">
         <v>4</v>
       </c>
       <c r="E170" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G170">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="H170">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I170">
         <v>1</v>
@@ -4947,22 +4898,22 @@
     </row>
     <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C171">
-        <v>7629</v>
+        <v>7637</v>
       </c>
       <c r="D171" t="s">
         <v>4</v>
       </c>
       <c r="E171" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G171">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H171">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I171">
         <v>1</v>
@@ -4970,22 +4921,22 @@
     </row>
     <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B172">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C172">
-        <v>7630</v>
+        <v>7638</v>
       </c>
       <c r="D172" t="s">
         <v>4</v>
       </c>
       <c r="E172" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G172">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H172">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I172">
         <v>1</v>
@@ -4993,22 +4944,22 @@
     </row>
     <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B173">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C173">
-        <v>7631</v>
+        <v>7639</v>
       </c>
       <c r="D173" t="s">
         <v>4</v>
       </c>
       <c r="E173" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G173">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H173">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I173">
         <v>1</v>
@@ -5016,22 +4967,22 @@
     </row>
     <row r="174" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B174">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C174">
-        <v>7632</v>
+        <v>7640</v>
       </c>
       <c r="D174" t="s">
         <v>4</v>
       </c>
       <c r="E174" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G174">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H174">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I174">
         <v>1</v>
@@ -5039,22 +4990,22 @@
     </row>
     <row r="175" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B175">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C175">
-        <v>7633</v>
+        <v>7641</v>
       </c>
       <c r="D175" t="s">
         <v>4</v>
       </c>
       <c r="E175" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G175">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="H175">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I175">
         <v>1</v>
@@ -5062,22 +5013,22 @@
     </row>
     <row r="176" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B176">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C176">
-        <v>7634</v>
+        <v>7642</v>
       </c>
       <c r="D176" t="s">
         <v>4</v>
       </c>
       <c r="E176" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G176">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H176">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I176">
         <v>1</v>
@@ -5085,22 +5036,22 @@
     </row>
     <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C177">
-        <v>7635</v>
+        <v>7643</v>
       </c>
       <c r="D177" t="s">
         <v>4</v>
       </c>
       <c r="E177" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G177">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="H177">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="I177">
         <v>1</v>
@@ -5108,22 +5059,22 @@
     </row>
     <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C178">
-        <v>7636</v>
+        <v>7644</v>
       </c>
       <c r="D178" t="s">
         <v>4</v>
       </c>
       <c r="E178" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G178">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H178">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I178">
         <v>1</v>
@@ -5131,22 +5082,22 @@
     </row>
     <row r="179" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B179">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C179">
-        <v>7637</v>
+        <v>7645</v>
       </c>
       <c r="D179" t="s">
         <v>4</v>
       </c>
       <c r="E179" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G179">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="H179">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="I179">
         <v>1</v>
@@ -5154,22 +5105,22 @@
     </row>
     <row r="180" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B180">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C180">
-        <v>7638</v>
+        <v>7646</v>
       </c>
       <c r="D180" t="s">
         <v>4</v>
       </c>
       <c r="E180" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G180">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="H180">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="I180">
         <v>1</v>
@@ -5177,22 +5128,22 @@
     </row>
     <row r="181" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B181">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C181">
-        <v>7639</v>
+        <v>7647</v>
       </c>
       <c r="D181" t="s">
         <v>4</v>
       </c>
       <c r="E181" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G181">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H181">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I181">
         <v>1</v>
@@ -5200,22 +5151,22 @@
     </row>
     <row r="182" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B182">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C182">
-        <v>7640</v>
+        <v>7648</v>
       </c>
       <c r="D182" t="s">
         <v>4</v>
       </c>
       <c r="E182" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G182">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H182">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I182">
         <v>1</v>
@@ -5223,22 +5174,22 @@
     </row>
     <row r="183" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B183">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C183">
-        <v>7641</v>
+        <v>7649</v>
       </c>
       <c r="D183" t="s">
         <v>4</v>
       </c>
       <c r="E183" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G183">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="H183">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="I183">
         <v>1</v>
@@ -5246,217 +5197,223 @@
     </row>
     <row r="184" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B184">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C184">
-        <v>7642</v>
+        <v>7650</v>
       </c>
       <c r="D184" t="s">
         <v>4</v>
       </c>
       <c r="E184" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G184">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H184">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I184">
         <v>1</v>
       </c>
     </row>
     <row r="185" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B185">
-        <v>442</v>
-      </c>
-      <c r="C185">
-        <v>7643</v>
-      </c>
-      <c r="D185" t="s">
-        <v>4</v>
-      </c>
-      <c r="E185" t="s">
-        <v>33</v>
-      </c>
-      <c r="G185">
-        <v>5</v>
-      </c>
-      <c r="H185">
-        <v>5</v>
-      </c>
-      <c r="I185">
+      <c r="B185" s="18">
+        <v>450</v>
+      </c>
+      <c r="C185" s="18">
+        <v>8001</v>
+      </c>
+      <c r="D185" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E185" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F185" s="18">
+        <v>40001</v>
+      </c>
+      <c r="G185" s="18">
+        <v>1</v>
+      </c>
+      <c r="H185" s="18">
+        <v>1</v>
+      </c>
+      <c r="I185" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="186" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B186">
-        <v>443</v>
-      </c>
-      <c r="C186">
-        <v>7644</v>
-      </c>
-      <c r="D186" t="s">
-        <v>4</v>
-      </c>
-      <c r="E186" t="s">
-        <v>34</v>
-      </c>
-      <c r="G186">
-        <v>3</v>
-      </c>
-      <c r="H186">
-        <v>3</v>
-      </c>
-      <c r="I186">
+      <c r="B186" s="18">
+        <v>451</v>
+      </c>
+      <c r="C186" s="18">
+        <v>8001</v>
+      </c>
+      <c r="D186" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E186" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G186" s="18">
+        <v>300</v>
+      </c>
+      <c r="H186" s="18">
+        <v>600</v>
+      </c>
+      <c r="I186" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B187">
-        <v>444</v>
-      </c>
-      <c r="C187">
-        <v>7645</v>
-      </c>
-      <c r="D187" t="s">
-        <v>4</v>
-      </c>
-      <c r="E187" t="s">
-        <v>26</v>
-      </c>
-      <c r="G187">
-        <v>300</v>
-      </c>
-      <c r="H187">
-        <v>300</v>
-      </c>
-      <c r="I187">
+      <c r="B187" s="18">
+        <v>452</v>
+      </c>
+      <c r="C187" s="18">
+        <v>8002</v>
+      </c>
+      <c r="D187" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E187" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F187" s="18">
+        <v>40002</v>
+      </c>
+      <c r="G187" s="18">
+        <v>1</v>
+      </c>
+      <c r="H187" s="18">
+        <v>1</v>
+      </c>
+      <c r="I187" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="188" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B188">
-        <v>445</v>
-      </c>
-      <c r="C188">
-        <v>7646</v>
-      </c>
-      <c r="D188" t="s">
-        <v>4</v>
-      </c>
-      <c r="E188" t="s">
+      <c r="B188" s="18">
+        <v>453</v>
+      </c>
+      <c r="C188" s="18">
+        <v>8002</v>
+      </c>
+      <c r="D188" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E188" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G188">
-        <v>10000</v>
-      </c>
-      <c r="H188">
-        <v>10000</v>
-      </c>
-      <c r="I188">
+      <c r="G188" s="18">
+        <v>600</v>
+      </c>
+      <c r="H188" s="18">
+        <v>1200</v>
+      </c>
+      <c r="I188" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="189" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B189">
-        <v>446</v>
-      </c>
-      <c r="C189">
-        <v>7647</v>
-      </c>
-      <c r="D189" t="s">
-        <v>4</v>
-      </c>
-      <c r="E189" t="s">
-        <v>32</v>
-      </c>
-      <c r="G189">
-        <v>5</v>
-      </c>
-      <c r="H189">
-        <v>5</v>
-      </c>
-      <c r="I189">
+      <c r="B189" s="18">
+        <v>454</v>
+      </c>
+      <c r="C189" s="18">
+        <v>8101</v>
+      </c>
+      <c r="D189" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E189" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G189" s="18">
+        <v>2000</v>
+      </c>
+      <c r="H189" s="18">
+        <v>2000</v>
+      </c>
+      <c r="I189" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="190" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B190">
-        <v>447</v>
-      </c>
-      <c r="C190">
-        <v>7648</v>
-      </c>
-      <c r="D190" t="s">
-        <v>4</v>
-      </c>
-      <c r="E190" t="s">
-        <v>33</v>
-      </c>
-      <c r="G190">
-        <v>5</v>
-      </c>
-      <c r="H190">
-        <v>5</v>
-      </c>
-      <c r="I190">
+      <c r="B190" s="18">
+        <v>455</v>
+      </c>
+      <c r="C190" s="18">
+        <v>8102</v>
+      </c>
+      <c r="D190" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E190" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G190" s="18">
+        <v>4000</v>
+      </c>
+      <c r="H190" s="18">
+        <v>4000</v>
+      </c>
+      <c r="I190" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="191" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B191">
-        <v>448</v>
-      </c>
-      <c r="C191">
-        <v>7649</v>
-      </c>
-      <c r="D191" t="s">
-        <v>4</v>
-      </c>
-      <c r="E191" t="s">
-        <v>34</v>
-      </c>
-      <c r="G191">
-        <v>3</v>
-      </c>
-      <c r="H191">
-        <v>3</v>
-      </c>
-      <c r="I191">
+      <c r="B191" s="18">
+        <v>456</v>
+      </c>
+      <c r="C191" s="18">
+        <v>8103</v>
+      </c>
+      <c r="D191" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E191" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G191" s="18">
+        <v>6000</v>
+      </c>
+      <c r="H191" s="18">
+        <v>6000</v>
+      </c>
+      <c r="I191" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B192">
-        <v>449</v>
-      </c>
-      <c r="C192">
-        <v>7650</v>
-      </c>
-      <c r="D192" t="s">
-        <v>4</v>
-      </c>
-      <c r="E192" t="s">
-        <v>31</v>
-      </c>
-      <c r="G192">
-        <v>3</v>
-      </c>
-      <c r="H192">
-        <v>3</v>
-      </c>
-      <c r="I192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B192" s="18">
+        <v>457</v>
+      </c>
+      <c r="C192" s="18">
+        <v>8104</v>
+      </c>
+      <c r="D192" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E192" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G192" s="18">
+        <v>8000</v>
+      </c>
+      <c r="H192" s="18">
+        <v>8000</v>
+      </c>
+      <c r="I192" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B193" s="18">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C193" s="18">
-        <v>8001</v>
+        <v>8201</v>
       </c>
       <c r="D193" s="18" t="s">
         <v>3</v>
@@ -5477,12 +5434,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B194" s="18">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C194" s="18">
-        <v>8001</v>
+        <v>8202</v>
       </c>
       <c r="D194" s="18" t="s">
         <v>4</v>
@@ -5491,116 +5448,116 @@
         <v>21</v>
       </c>
       <c r="G194" s="18">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H194" s="18">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="I194" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B195" s="18">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C195" s="18">
-        <v>8002</v>
+        <v>8203</v>
       </c>
       <c r="D195" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E195" s="18">
+        <v>4</v>
+      </c>
+      <c r="E195" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G195" s="18">
+        <v>3</v>
+      </c>
+      <c r="H195" s="18">
+        <v>5</v>
+      </c>
+      <c r="I195" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B196" s="18">
+        <v>461</v>
+      </c>
+      <c r="C196" s="18">
+        <v>8203</v>
+      </c>
+      <c r="D196" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E196" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G196" s="18">
+        <v>3</v>
+      </c>
+      <c r="H196" s="18">
+        <v>5</v>
+      </c>
+      <c r="I196" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B197" s="18">
+        <v>462</v>
+      </c>
+      <c r="C197" s="18">
+        <v>8203</v>
+      </c>
+      <c r="D197" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E197" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G197" s="18">
+        <v>3</v>
+      </c>
+      <c r="H197" s="18">
+        <v>5</v>
+      </c>
+      <c r="I197" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B198" s="18">
+        <v>463</v>
+      </c>
+      <c r="C198" s="18">
+        <v>8211</v>
+      </c>
+      <c r="D198" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E198" s="18">
         <v>3001</v>
       </c>
-      <c r="F195" s="18">
+      <c r="F198" s="18">
         <v>40002</v>
       </c>
-      <c r="G195" s="18">
-        <v>1</v>
-      </c>
-      <c r="H195" s="18">
-        <v>1</v>
-      </c>
-      <c r="I195" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B196" s="18">
-        <v>453</v>
-      </c>
-      <c r="C196" s="18">
-        <v>8002</v>
-      </c>
-      <c r="D196" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E196" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G196" s="18">
-        <v>600</v>
-      </c>
-      <c r="H196" s="18">
-        <v>1200</v>
-      </c>
-      <c r="I196" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B197" s="18">
-        <v>454</v>
-      </c>
-      <c r="C197" s="18">
-        <v>8101</v>
-      </c>
-      <c r="D197" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E197" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G197" s="18">
-        <v>2000</v>
-      </c>
-      <c r="H197" s="18">
-        <v>2000</v>
-      </c>
-      <c r="I197" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B198" s="18">
-        <v>455</v>
-      </c>
-      <c r="C198" s="18">
-        <v>8102</v>
-      </c>
-      <c r="D198" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E198" s="18" t="s">
-        <v>21</v>
-      </c>
       <c r="G198" s="18">
-        <v>4000</v>
+        <v>1</v>
       </c>
       <c r="H198" s="18">
-        <v>4000</v>
+        <v>1</v>
       </c>
       <c r="I198" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B199" s="18">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C199" s="18">
-        <v>8103</v>
+        <v>8212</v>
       </c>
       <c r="D199" s="18" t="s">
         <v>4</v>
@@ -5609,295 +5566,316 @@
         <v>21</v>
       </c>
       <c r="G199" s="18">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="H199" s="18">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="I199" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B200" s="18">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C200" s="18">
-        <v>8104</v>
+        <v>8213</v>
       </c>
       <c r="D200" s="18" t="s">
         <v>4</v>
       </c>
       <c r="E200" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G200" s="18">
+        <v>8</v>
+      </c>
+      <c r="H200" s="18">
+        <v>12</v>
+      </c>
+      <c r="I200" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B201" s="18">
+        <v>466</v>
+      </c>
+      <c r="C201" s="18">
+        <v>8213</v>
+      </c>
+      <c r="D201" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E201" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G201" s="18">
+        <v>8</v>
+      </c>
+      <c r="H201" s="18">
+        <v>12</v>
+      </c>
+      <c r="I201" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B202" s="18">
+        <v>467</v>
+      </c>
+      <c r="C202" s="18">
+        <v>8213</v>
+      </c>
+      <c r="D202" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E202" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G202" s="18">
+        <v>8</v>
+      </c>
+      <c r="H202" s="18">
+        <v>12</v>
+      </c>
+      <c r="I202" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B203" s="18">
+        <v>468</v>
+      </c>
+      <c r="C203" s="18">
+        <v>8003</v>
+      </c>
+      <c r="D203" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E203" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F203" s="18">
+        <v>40003</v>
+      </c>
+      <c r="G203" s="18">
+        <v>1</v>
+      </c>
+      <c r="H203" s="18">
+        <v>1</v>
+      </c>
+      <c r="I203" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B204" s="18">
+        <v>469</v>
+      </c>
+      <c r="C204" s="18">
+        <v>8003</v>
+      </c>
+      <c r="D204" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E204" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G200" s="18">
-        <v>8000</v>
-      </c>
-      <c r="H200" s="18">
-        <v>8000</v>
-      </c>
-      <c r="I200" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B201" s="18">
-        <v>458</v>
-      </c>
-      <c r="C201" s="18">
-        <v>8201</v>
-      </c>
-      <c r="D201" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E201" s="18">
+      <c r="G204" s="18">
+        <v>1000</v>
+      </c>
+      <c r="H204" s="18">
+        <v>2000</v>
+      </c>
+      <c r="I204" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B205" s="18">
+        <v>470</v>
+      </c>
+      <c r="C205" s="18">
+        <v>8004</v>
+      </c>
+      <c r="D205" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E205" s="18">
         <v>3001</v>
       </c>
-      <c r="F201" s="18">
-        <v>40001</v>
-      </c>
-      <c r="G201" s="18">
-        <v>1</v>
-      </c>
-      <c r="H201" s="18">
-        <v>1</v>
-      </c>
-      <c r="I201" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B202" s="18">
-        <v>459</v>
-      </c>
-      <c r="C202" s="18">
-        <v>8202</v>
-      </c>
-      <c r="D202" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E202" s="18" t="s">
+      <c r="F205" s="18">
+        <v>40003</v>
+      </c>
+      <c r="G205" s="18">
+        <v>1</v>
+      </c>
+      <c r="H205" s="18">
+        <v>1</v>
+      </c>
+      <c r="I205" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B206" s="18">
+        <v>471</v>
+      </c>
+      <c r="C206" s="18">
+        <v>8004</v>
+      </c>
+      <c r="D206" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E206" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G202" s="18">
-        <v>1000</v>
-      </c>
-      <c r="H202" s="18">
+      <c r="G206" s="18">
         <v>2000</v>
       </c>
-      <c r="I202" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B203" s="18">
-        <v>460</v>
-      </c>
-      <c r="C203" s="18">
-        <v>8203</v>
-      </c>
-      <c r="D203" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E203" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G203" s="18">
-        <v>3</v>
-      </c>
-      <c r="H203" s="18">
-        <v>5</v>
-      </c>
-      <c r="I203" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B204" s="18">
-        <v>461</v>
-      </c>
-      <c r="C204" s="18">
-        <v>8203</v>
-      </c>
-      <c r="D204" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E204" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G204" s="18">
-        <v>3</v>
-      </c>
-      <c r="H204" s="18">
-        <v>5</v>
-      </c>
-      <c r="I204" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B205" s="18">
-        <v>462</v>
-      </c>
-      <c r="C205" s="18">
-        <v>8203</v>
-      </c>
-      <c r="D205" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E205" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G205" s="18">
-        <v>3</v>
-      </c>
-      <c r="H205" s="18">
-        <v>5</v>
-      </c>
-      <c r="I205" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B206" s="18">
-        <v>463</v>
-      </c>
-      <c r="C206" s="18">
-        <v>8211</v>
-      </c>
-      <c r="D206" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E206" s="18">
-        <v>3001</v>
-      </c>
-      <c r="F206" s="18">
-        <v>40002</v>
-      </c>
-      <c r="G206" s="18">
-        <v>1</v>
-      </c>
       <c r="H206" s="18">
-        <v>1</v>
+        <v>4000</v>
       </c>
       <c r="I206" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B207" s="18">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C207" s="18">
-        <v>8212</v>
+        <v>100</v>
       </c>
       <c r="D207" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E207" s="18" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="E207" s="18">
+        <v>1010101001</v>
       </c>
       <c r="G207" s="18">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="H207" s="18">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="I207" s="18">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J207" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K207" s="18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="208" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B208" s="18">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C208" s="18">
-        <v>8213</v>
+        <v>100</v>
       </c>
       <c r="D208" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E208" s="18" t="s">
-        <v>28</v>
+        <v>2</v>
+      </c>
+      <c r="E208" s="18">
+        <v>1010101002</v>
       </c>
       <c r="G208" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H208" s="18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I208" s="18">
         <v>1</v>
+      </c>
+      <c r="J208" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K208" s="18">
+        <v>50</v>
       </c>
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B209" s="18">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C209" s="18">
-        <v>8213</v>
+        <v>100</v>
       </c>
       <c r="D209" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E209" s="18" t="s">
-        <v>29</v>
+        <v>2</v>
+      </c>
+      <c r="E209" s="18">
+        <v>1010101003</v>
       </c>
       <c r="G209" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H209" s="18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I209" s="18">
         <v>1</v>
+      </c>
+      <c r="J209" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K209" s="18">
+        <v>50</v>
       </c>
     </row>
     <row r="210" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B210" s="18">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C210" s="18">
-        <v>8213</v>
+        <v>100</v>
       </c>
       <c r="D210" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E210" s="18" t="s">
-        <v>32</v>
+        <v>2</v>
+      </c>
+      <c r="E210" s="18">
+        <v>1010101004</v>
       </c>
       <c r="G210" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H210" s="18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I210" s="18">
         <v>1</v>
+      </c>
+      <c r="J210" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K210" s="18">
+        <v>50</v>
       </c>
     </row>
     <row r="211" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B211" s="18">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C211" s="18">
-        <v>8003</v>
+        <v>100</v>
       </c>
       <c r="D211" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E211" s="18">
-        <v>3001</v>
-      </c>
-      <c r="F211" s="18">
-        <v>40003</v>
+        <v>4</v>
+      </c>
+      <c r="E211" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="G211" s="18">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="H211" s="18">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="I211" s="18">
         <v>1</v>
@@ -5905,22 +5883,22 @@
     </row>
     <row r="212" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B212" s="18">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C212" s="18">
-        <v>8003</v>
+        <v>100</v>
       </c>
       <c r="D212" s="18" t="s">
         <v>4</v>
       </c>
       <c r="E212" s="18" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G212" s="18">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="H212" s="18">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="I212" s="18">
         <v>1</v>
@@ -5928,25 +5906,22 @@
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B213" s="18">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C213" s="18">
-        <v>8004</v>
+        <v>8301</v>
       </c>
       <c r="D213" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E213" s="18">
-        <v>3001</v>
-      </c>
-      <c r="F213" s="18">
-        <v>40003</v>
+        <v>4</v>
+      </c>
+      <c r="E213" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="G213" s="18">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="H213" s="18">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="I213" s="18">
         <v>1</v>
@@ -5954,68 +5929,68 @@
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B214" s="18">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="C214" s="18">
-        <v>8004</v>
+        <v>8301</v>
       </c>
       <c r="D214" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E214" s="18" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="E214" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F214" s="18">
+        <v>10001</v>
       </c>
       <c r="G214" s="18">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="H214" s="18">
-        <v>4000</v>
+        <v>1</v>
       </c>
       <c r="I214" s="18">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B215" s="18">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C215" s="18">
-        <v>100</v>
+        <v>8302</v>
       </c>
       <c r="D215" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E215" s="18">
-        <v>1010101001</v>
+        <v>4</v>
+      </c>
+      <c r="E215" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="G215" s="18">
-        <v>1</v>
+        <v>4000</v>
       </c>
       <c r="H215" s="18">
-        <v>1</v>
+        <v>6000</v>
       </c>
       <c r="I215" s="18">
         <v>1</v>
-      </c>
-      <c r="J215" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="K215" s="18">
-        <v>50</v>
       </c>
     </row>
     <row r="216" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B216" s="18">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C216" s="18">
-        <v>100</v>
+        <v>8302</v>
       </c>
       <c r="D216" s="18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E216" s="18">
-        <v>1010101002</v>
+        <v>3001</v>
+      </c>
+      <c r="F216" s="18">
+        <v>10001</v>
       </c>
       <c r="G216" s="18">
         <v>1</v>
@@ -6024,56 +5999,47 @@
         <v>1</v>
       </c>
       <c r="I216" s="18">
-        <v>1</v>
-      </c>
-      <c r="J216" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="K216" s="18">
-        <v>50</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="217" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B217" s="18">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C217" s="18">
-        <v>100</v>
+        <v>8303</v>
       </c>
       <c r="D217" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E217" s="18">
-        <v>1010101003</v>
+        <v>4</v>
+      </c>
+      <c r="E217" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="G217" s="18">
-        <v>1</v>
+        <v>6000</v>
       </c>
       <c r="H217" s="18">
-        <v>1</v>
+        <v>9000</v>
       </c>
       <c r="I217" s="18">
         <v>1</v>
-      </c>
-      <c r="J217" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="K217" s="18">
-        <v>50</v>
       </c>
     </row>
     <row r="218" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B218" s="18">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C218" s="18">
-        <v>100</v>
+        <v>8303</v>
       </c>
       <c r="D218" s="18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E218" s="18">
-        <v>1010101004</v>
+        <v>3001</v>
+      </c>
+      <c r="F218" s="18">
+        <v>10001</v>
       </c>
       <c r="G218" s="18">
         <v>1</v>
@@ -6082,21 +6048,15 @@
         <v>1</v>
       </c>
       <c r="I218" s="18">
-        <v>1</v>
-      </c>
-      <c r="J218" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="K218" s="18">
-        <v>50</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="219" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B219" s="18">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="C219" s="18">
-        <v>100</v>
+        <v>8304</v>
       </c>
       <c r="D219" s="18" t="s">
         <v>4</v>
@@ -6105,10 +6065,10 @@
         <v>21</v>
       </c>
       <c r="G219" s="18">
-        <v>100000</v>
+        <v>8000</v>
       </c>
       <c r="H219" s="18">
-        <v>100000</v>
+        <v>12000</v>
       </c>
       <c r="I219" s="18">
         <v>1</v>
@@ -6116,33 +6076,36 @@
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B220" s="18">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C220" s="18">
-        <v>100</v>
+        <v>8304</v>
       </c>
       <c r="D220" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E220" s="18" t="s">
-        <v>26</v>
+        <v>3</v>
+      </c>
+      <c r="E220" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F220" s="18">
+        <v>10001</v>
       </c>
       <c r="G220" s="18">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="H220" s="18">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="I220" s="18">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="221" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B221" s="18">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C221" s="18">
-        <v>8301</v>
+        <v>8305</v>
       </c>
       <c r="D221" s="18" t="s">
         <v>4</v>
@@ -6151,10 +6114,10 @@
         <v>21</v>
       </c>
       <c r="G221" s="18">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="H221" s="18">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="I221" s="18">
         <v>1</v>
@@ -6162,10 +6125,10 @@
     </row>
     <row r="222" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B222" s="18">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C222" s="18">
-        <v>8301</v>
+        <v>8305</v>
       </c>
       <c r="D222" s="18" t="s">
         <v>3</v>
@@ -6188,10 +6151,10 @@
     </row>
     <row r="223" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B223" s="18">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C223" s="18">
-        <v>8302</v>
+        <v>8306</v>
       </c>
       <c r="D223" s="18" t="s">
         <v>4</v>
@@ -6200,10 +6163,10 @@
         <v>21</v>
       </c>
       <c r="G223" s="18">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="H223" s="18">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="I223" s="18">
         <v>1</v>
@@ -6211,10 +6174,10 @@
     </row>
     <row r="224" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B224" s="18">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C224" s="18">
-        <v>8302</v>
+        <v>8306</v>
       </c>
       <c r="D224" s="18" t="s">
         <v>3</v>
@@ -6223,7 +6186,7 @@
         <v>3001</v>
       </c>
       <c r="F224" s="18">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="G224" s="18">
         <v>1</v>
@@ -6237,10 +6200,10 @@
     </row>
     <row r="225" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B225" s="18">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C225" s="18">
-        <v>8303</v>
+        <v>8307</v>
       </c>
       <c r="D225" s="18" t="s">
         <v>4</v>
@@ -6249,10 +6212,10 @@
         <v>21</v>
       </c>
       <c r="G225" s="18">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H225" s="18">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="I225" s="18">
         <v>1</v>
@@ -6260,10 +6223,10 @@
     </row>
     <row r="226" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B226" s="18">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C226" s="18">
-        <v>8303</v>
+        <v>8307</v>
       </c>
       <c r="D226" s="18" t="s">
         <v>3</v>
@@ -6272,7 +6235,7 @@
         <v>3001</v>
       </c>
       <c r="F226" s="18">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="G226" s="18">
         <v>1</v>
@@ -6286,10 +6249,10 @@
     </row>
     <row r="227" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B227" s="18">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C227" s="18">
-        <v>8304</v>
+        <v>8308</v>
       </c>
       <c r="D227" s="18" t="s">
         <v>4</v>
@@ -6298,10 +6261,10 @@
         <v>21</v>
       </c>
       <c r="G227" s="18">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="H227" s="18">
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="I227" s="18">
         <v>1</v>
@@ -6309,10 +6272,10 @@
     </row>
     <row r="228" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B228" s="18">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C228" s="18">
-        <v>8304</v>
+        <v>8308</v>
       </c>
       <c r="D228" s="18" t="s">
         <v>3</v>
@@ -6321,7 +6284,7 @@
         <v>3001</v>
       </c>
       <c r="F228" s="18">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="G228" s="18">
         <v>1</v>
@@ -6335,10 +6298,10 @@
     </row>
     <row r="229" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B229" s="18">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C229" s="18">
-        <v>8305</v>
+        <v>8309</v>
       </c>
       <c r="D229" s="18" t="s">
         <v>4</v>
@@ -6347,10 +6310,10 @@
         <v>21</v>
       </c>
       <c r="G229" s="18">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="H229" s="18">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I229" s="18">
         <v>1</v>
@@ -6358,10 +6321,10 @@
     </row>
     <row r="230" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B230" s="18">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C230" s="18">
-        <v>8305</v>
+        <v>8309</v>
       </c>
       <c r="D230" s="18" t="s">
         <v>3</v>
@@ -6370,7 +6333,7 @@
         <v>3001</v>
       </c>
       <c r="F230" s="18">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="G230" s="18">
         <v>1</v>
@@ -6384,10 +6347,10 @@
     </row>
     <row r="231" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B231" s="18">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C231" s="18">
-        <v>8306</v>
+        <v>8310</v>
       </c>
       <c r="D231" s="18" t="s">
         <v>4</v>
@@ -6396,10 +6359,10 @@
         <v>21</v>
       </c>
       <c r="G231" s="18">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="H231" s="18">
-        <v>18000</v>
+        <v>30000</v>
       </c>
       <c r="I231" s="18">
         <v>1</v>
@@ -6407,10 +6370,10 @@
     </row>
     <row r="232" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B232" s="18">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C232" s="18">
-        <v>8306</v>
+        <v>8310</v>
       </c>
       <c r="D232" s="18" t="s">
         <v>3</v>
@@ -6433,10 +6396,10 @@
     </row>
     <row r="233" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B233" s="18">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C233" s="18">
-        <v>8307</v>
+        <v>8311</v>
       </c>
       <c r="D233" s="18" t="s">
         <v>4</v>
@@ -6445,10 +6408,10 @@
         <v>21</v>
       </c>
       <c r="G233" s="18">
-        <v>14000</v>
+        <v>22000</v>
       </c>
       <c r="H233" s="18">
-        <v>21000</v>
+        <v>33000</v>
       </c>
       <c r="I233" s="18">
         <v>1</v>
@@ -6456,10 +6419,10 @@
     </row>
     <row r="234" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B234" s="18">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C234" s="18">
-        <v>8307</v>
+        <v>8311</v>
       </c>
       <c r="D234" s="18" t="s">
         <v>3</v>
@@ -6468,7 +6431,7 @@
         <v>3001</v>
       </c>
       <c r="F234" s="18">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="G234" s="18">
         <v>1</v>
@@ -6482,10 +6445,10 @@
     </row>
     <row r="235" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B235" s="18">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C235" s="18">
-        <v>8308</v>
+        <v>8312</v>
       </c>
       <c r="D235" s="18" t="s">
         <v>4</v>
@@ -6494,10 +6457,10 @@
         <v>21</v>
       </c>
       <c r="G235" s="18">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="H235" s="18">
-        <v>24000</v>
+        <v>36000</v>
       </c>
       <c r="I235" s="18">
         <v>1</v>
@@ -6505,10 +6468,10 @@
     </row>
     <row r="236" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B236" s="18">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C236" s="18">
-        <v>8308</v>
+        <v>8312</v>
       </c>
       <c r="D236" s="18" t="s">
         <v>3</v>
@@ -6517,7 +6480,7 @@
         <v>3001</v>
       </c>
       <c r="F236" s="18">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="G236" s="18">
         <v>1</v>
@@ -6531,10 +6494,10 @@
     </row>
     <row r="237" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B237" s="18">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="C237" s="18">
-        <v>8309</v>
+        <v>8313</v>
       </c>
       <c r="D237" s="18" t="s">
         <v>4</v>
@@ -6543,10 +6506,10 @@
         <v>21</v>
       </c>
       <c r="G237" s="18">
-        <v>18000</v>
+        <v>26000</v>
       </c>
       <c r="H237" s="18">
-        <v>27000</v>
+        <v>39000</v>
       </c>
       <c r="I237" s="18">
         <v>1</v>
@@ -6554,10 +6517,10 @@
     </row>
     <row r="238" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B238" s="18">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C238" s="18">
-        <v>8309</v>
+        <v>8313</v>
       </c>
       <c r="D238" s="18" t="s">
         <v>3</v>
@@ -6566,7 +6529,7 @@
         <v>3001</v>
       </c>
       <c r="F238" s="18">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="G238" s="18">
         <v>1</v>
@@ -6580,10 +6543,10 @@
     </row>
     <row r="239" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B239" s="18">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C239" s="18">
-        <v>8310</v>
+        <v>8314</v>
       </c>
       <c r="D239" s="18" t="s">
         <v>4</v>
@@ -6592,10 +6555,10 @@
         <v>21</v>
       </c>
       <c r="G239" s="18">
-        <v>20000</v>
+        <v>28000</v>
       </c>
       <c r="H239" s="18">
-        <v>30000</v>
+        <v>42000</v>
       </c>
       <c r="I239" s="18">
         <v>1</v>
@@ -6603,10 +6566,10 @@
     </row>
     <row r="240" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B240" s="18">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="C240" s="18">
-        <v>8310</v>
+        <v>8314</v>
       </c>
       <c r="D240" s="18" t="s">
         <v>3</v>
@@ -6615,7 +6578,7 @@
         <v>3001</v>
       </c>
       <c r="F240" s="18">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="G240" s="18">
         <v>1</v>
@@ -6629,10 +6592,10 @@
     </row>
     <row r="241" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B241" s="18">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C241" s="18">
-        <v>8311</v>
+        <v>8315</v>
       </c>
       <c r="D241" s="18" t="s">
         <v>4</v>
@@ -6641,10 +6604,10 @@
         <v>21</v>
       </c>
       <c r="G241" s="18">
-        <v>22000</v>
+        <v>30000</v>
       </c>
       <c r="H241" s="18">
-        <v>33000</v>
+        <v>45000</v>
       </c>
       <c r="I241" s="18">
         <v>1</v>
@@ -6652,10 +6615,10 @@
     </row>
     <row r="242" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B242" s="18">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C242" s="18">
-        <v>8311</v>
+        <v>8315</v>
       </c>
       <c r="D242" s="18" t="s">
         <v>3</v>
@@ -6678,22 +6641,22 @@
     </row>
     <row r="243" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B243" s="18">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="C243" s="18">
-        <v>8312</v>
+        <v>100</v>
       </c>
       <c r="D243" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E243" s="18" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="E243" s="18">
+        <v>1020100001</v>
       </c>
       <c r="G243" s="18">
-        <v>24000</v>
+        <v>10</v>
       </c>
       <c r="H243" s="18">
-        <v>36000</v>
+        <v>10</v>
       </c>
       <c r="I243" s="18">
         <v>1</v>
@@ -6701,48 +6664,45 @@
     </row>
     <row r="244" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B244" s="18">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C244" s="18">
-        <v>8312</v>
+        <v>100</v>
       </c>
       <c r="D244" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E244" s="18">
-        <v>3001</v>
-      </c>
-      <c r="F244" s="18">
-        <v>10003</v>
+        <v>1020100002</v>
       </c>
       <c r="G244" s="18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H244" s="18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I244" s="18">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B245" s="18">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C245" s="18">
-        <v>8313</v>
+        <v>100</v>
       </c>
       <c r="D245" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E245" s="18" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="E245" s="18">
+        <v>1020100003</v>
       </c>
       <c r="G245" s="18">
-        <v>26000</v>
+        <v>10</v>
       </c>
       <c r="H245" s="18">
-        <v>39000</v>
+        <v>10</v>
       </c>
       <c r="I245" s="18">
         <v>1</v>
@@ -6750,48 +6710,48 @@
     </row>
     <row r="246" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B246" s="18">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C246" s="18">
-        <v>8313</v>
+        <v>9101</v>
       </c>
       <c r="D246" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E246" s="18">
-        <v>3001</v>
-      </c>
-      <c r="F246" s="18">
-        <v>10003</v>
+        <v>4</v>
+      </c>
+      <c r="E246" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="G246" s="18">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="H246" s="18">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="I246" s="18">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B247" s="18">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C247" s="18">
-        <v>8314</v>
+        <v>9101</v>
       </c>
       <c r="D247" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E247" s="18" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="E247" s="18">
+        <v>3001</v>
+      </c>
+      <c r="F247" s="18">
+        <v>40002</v>
       </c>
       <c r="G247" s="18">
-        <v>28000</v>
+        <v>1</v>
       </c>
       <c r="H247" s="18">
-        <v>42000</v>
+        <v>1</v>
       </c>
       <c r="I247" s="18">
         <v>1</v>
@@ -6799,19 +6759,16 @@
     </row>
     <row r="248" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B248" s="18">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C248" s="18">
-        <v>8314</v>
+        <v>4101</v>
       </c>
       <c r="D248" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E248" s="18">
-        <v>3001</v>
-      </c>
-      <c r="F248" s="18">
-        <v>10003</v>
+        <v>1040200001</v>
       </c>
       <c r="G248" s="18">
         <v>1</v>
@@ -6820,27 +6777,27 @@
         <v>1</v>
       </c>
       <c r="I248" s="18">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B249" s="18">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C249" s="18">
-        <v>8315</v>
+        <v>4102</v>
       </c>
       <c r="D249" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E249" s="18" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="E249" s="18">
+        <v>1040200002</v>
       </c>
       <c r="G249" s="18">
-        <v>30000</v>
+        <v>1</v>
       </c>
       <c r="H249" s="18">
-        <v>45000</v>
+        <v>1</v>
       </c>
       <c r="I249" s="18">
         <v>1</v>
@@ -6848,19 +6805,16 @@
     </row>
     <row r="250" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B250" s="18">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C250" s="18">
-        <v>8315</v>
+        <v>4103</v>
       </c>
       <c r="D250" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E250" s="18">
-        <v>3001</v>
-      </c>
-      <c r="F250" s="18">
-        <v>10003</v>
+        <v>1040200003</v>
       </c>
       <c r="G250" s="18">
         <v>1</v>
@@ -6869,27 +6823,27 @@
         <v>1</v>
       </c>
       <c r="I250" s="18">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B251" s="18">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="C251" s="18">
-        <v>100</v>
+        <v>4104</v>
       </c>
       <c r="D251" s="18" t="s">
         <v>2</v>
       </c>
       <c r="E251" s="18">
-        <v>1020100001</v>
+        <v>1040200004</v>
       </c>
       <c r="G251" s="18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H251" s="18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I251" s="18">
         <v>1</v>
@@ -6897,22 +6851,22 @@
     </row>
     <row r="252" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B252" s="18">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C252" s="18">
-        <v>100</v>
+        <v>4105</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>2</v>
       </c>
       <c r="E252" s="18">
-        <v>1020100002</v>
+        <v>1040200005</v>
       </c>
       <c r="G252" s="18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H252" s="18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I252" s="18">
         <v>1</v>
@@ -6920,22 +6874,22 @@
     </row>
     <row r="253" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B253" s="18">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C253" s="18">
-        <v>100</v>
+        <v>4106</v>
       </c>
       <c r="D253" s="18" t="s">
         <v>2</v>
       </c>
       <c r="E253" s="18">
-        <v>1020100003</v>
+        <v>1040200006</v>
       </c>
       <c r="G253" s="18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H253" s="18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I253" s="18">
         <v>1</v>
@@ -6943,22 +6897,22 @@
     </row>
     <row r="254" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B254" s="18">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C254" s="18">
-        <v>9101</v>
+        <v>4201</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E254" s="18" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="E254" s="18">
+        <v>1040100002</v>
       </c>
       <c r="G254" s="18">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="H254" s="18">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="I254" s="18">
         <v>1</v>
@@ -6966,19 +6920,16 @@
     </row>
     <row r="255" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B255" s="18">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C255" s="18">
-        <v>9101</v>
+        <v>4202</v>
       </c>
       <c r="D255" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E255" s="18">
-        <v>3001</v>
-      </c>
-      <c r="F255" s="18">
-        <v>40002</v>
+        <v>1040100003</v>
       </c>
       <c r="G255" s="18">
         <v>1</v>
@@ -6992,10 +6943,10 @@
     </row>
     <row r="256" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B256" s="18">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C256" s="18">
-        <v>4101</v>
+        <v>9101</v>
       </c>
       <c r="D256" s="18" t="s">
         <v>2</v>
@@ -7010,21 +6961,21 @@
         <v>1</v>
       </c>
       <c r="I256" s="18">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="257" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B257" s="18">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C257" s="18">
-        <v>4102</v>
+        <v>4301</v>
       </c>
       <c r="D257" s="18" t="s">
         <v>2</v>
       </c>
       <c r="E257" s="18">
-        <v>1040200002</v>
+        <v>1030300001</v>
       </c>
       <c r="G257" s="18">
         <v>1</v>
@@ -7038,22 +6989,22 @@
     </row>
     <row r="258" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B258" s="18">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="C258" s="18">
-        <v>4103</v>
+        <v>4302</v>
       </c>
       <c r="D258" s="18" t="s">
         <v>2</v>
       </c>
       <c r="E258" s="18">
-        <v>1040200003</v>
+        <v>1030300001</v>
       </c>
       <c r="G258" s="18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H258" s="18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I258" s="18">
         <v>1</v>
@@ -7061,140 +7012,25 @@
     </row>
     <row r="259" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B259" s="18">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C259" s="18">
-        <v>4104</v>
+        <v>4303</v>
       </c>
       <c r="D259" s="18" t="s">
         <v>2</v>
       </c>
       <c r="E259" s="18">
-        <v>1040200004</v>
+        <v>1030300001</v>
       </c>
       <c r="G259" s="18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H259" s="18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I259" s="18">
         <v>1</v>
-      </c>
-    </row>
-    <row r="260" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B260" s="18">
-        <v>517</v>
-      </c>
-      <c r="C260" s="18">
-        <v>4105</v>
-      </c>
-      <c r="D260" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E260" s="18">
-        <v>1040200005</v>
-      </c>
-      <c r="G260" s="18">
-        <v>1</v>
-      </c>
-      <c r="H260" s="18">
-        <v>1</v>
-      </c>
-      <c r="I260" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B261" s="18">
-        <v>518</v>
-      </c>
-      <c r="C261" s="18">
-        <v>4106</v>
-      </c>
-      <c r="D261" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E261" s="18">
-        <v>1040200006</v>
-      </c>
-      <c r="G261" s="18">
-        <v>1</v>
-      </c>
-      <c r="H261" s="18">
-        <v>1</v>
-      </c>
-      <c r="I261" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="262" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B262" s="18">
-        <v>519</v>
-      </c>
-      <c r="C262" s="18">
-        <v>4201</v>
-      </c>
-      <c r="D262" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E262" s="18">
-        <v>1040100002</v>
-      </c>
-      <c r="G262" s="18">
-        <v>1</v>
-      </c>
-      <c r="H262" s="18">
-        <v>1</v>
-      </c>
-      <c r="I262" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="263" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B263" s="18">
-        <v>520</v>
-      </c>
-      <c r="C263" s="18">
-        <v>4202</v>
-      </c>
-      <c r="D263" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E263" s="18">
-        <v>1040100003</v>
-      </c>
-      <c r="G263" s="18">
-        <v>1</v>
-      </c>
-      <c r="H263" s="18">
-        <v>1</v>
-      </c>
-      <c r="I263" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B264" s="18">
-        <v>521</v>
-      </c>
-      <c r="C264" s="18">
-        <v>9101</v>
-      </c>
-      <c r="D264" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E264" s="18">
-        <v>1040200001</v>
-      </c>
-      <c r="G264" s="18">
-        <v>1</v>
-      </c>
-      <c r="H264" s="18">
-        <v>1</v>
-      </c>
-      <c r="I264" s="18">
-        <v>0.1</v>
       </c>
     </row>
   </sheetData>
